--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F8DD8B-058E-5243-AD7F-93951C825092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E9603-4402-324E-8C81-02F95F3E108E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -486,6 +486,12 @@
   </si>
   <si>
     <t>HG</t>
+  </si>
+  <si>
+    <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>NR</t>
   </si>
 </sst>
 </file>
@@ -873,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F67B87-FE0E-FC4A-8FE6-DAAF2AFECC8B}">
-  <dimension ref="A1:PW31"/>
+  <dimension ref="A1:PW32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -2205,11 +2211,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>240</v>
+        <v>330</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2225,11 +2231,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2241,11 +2247,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2356,13 +2362,22 @@
       <c r="CZ2" t="s">
         <v>149</v>
       </c>
+      <c r="DD2" t="s">
+        <v>149</v>
+      </c>
+      <c r="DG2">
+        <v>90</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>141</v>
+      </c>
       <c r="PS2" s="3">
         <f>COUNTIF(AI2:PR2,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT2" s="3">
         <f>COUNTIF(CY2:GX2,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU2" s="3">
         <f>COUNTIF(GY2:IT2,"HG")</f>
@@ -2383,11 +2398,11 @@
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C28" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D28" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
@@ -2403,11 +2418,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G28" si="9">SUM(H3:I3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H28" si="10">COUNTIF(AI3:PR3,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I28" si="11">COUNTIF(AI3:PR3,"R")</f>
@@ -2419,11 +2434,11 @@
       </c>
       <c r="K3">
         <f t="shared" ref="K3:K28" si="13">SUM(L3:M3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="3">
         <f t="shared" ref="L3:L28" si="14">COUNTIF(CY3:GX3,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="3">
         <f t="shared" ref="M3:M28" si="15">COUNTIF(CY3:GX3,"R")</f>
@@ -2519,13 +2534,22 @@
       <c r="CZ3" t="s">
         <v>141</v>
       </c>
+      <c r="DC3">
+        <v>90</v>
+      </c>
+      <c r="DD3" t="s">
+        <v>141</v>
+      </c>
+      <c r="DH3" t="s">
+        <v>149</v>
+      </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT28" si="33">COUNTIF(CY3:GX3,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU28" si="34">COUNTIF(GY3:IT3,"HG")</f>
@@ -2703,13 +2727,19 @@
       <c r="CZ4" t="s">
         <v>149</v>
       </c>
+      <c r="DD4" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>149</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
@@ -2730,11 +2760,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>360</v>
+        <v>523</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="D5">
         <f t="shared" si="6"/>
@@ -2750,11 +2780,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2766,11 +2796,11 @@
       </c>
       <c r="K5">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="3">
         <f t="shared" si="15"/>
@@ -2888,6 +2918,18 @@
         <v>90</v>
       </c>
       <c r="CZ5" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC5">
+        <v>73</v>
+      </c>
+      <c r="DD5" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG5">
+        <v>90</v>
+      </c>
+      <c r="DH5" t="s">
         <v>141</v>
       </c>
       <c r="PS5" s="3">
@@ -2917,11 +2959,11 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
@@ -2937,7 +2979,7 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
@@ -2945,15 +2987,15 @@
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="14"/>
@@ -2961,11 +3003,11 @@
       </c>
       <c r="M6" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
         <f t="shared" si="17"/>
@@ -3088,6 +3130,15 @@
       </c>
       <c r="CZ6" t="s">
         <v>142</v>
+      </c>
+      <c r="DC6">
+        <v>17</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>142</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>151</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
@@ -3255,13 +3306,19 @@
       <c r="CZ7" t="s">
         <v>149</v>
       </c>
+      <c r="DD7" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>149</v>
+      </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
@@ -3442,13 +3499,19 @@
       <c r="CZ8" t="s">
         <v>141</v>
       </c>
+      <c r="DD8" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH8" t="s">
+        <v>149</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="34"/>
@@ -3469,11 +3532,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>323</v>
+        <v>503</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
-        <v>78</v>
+        <v>258</v>
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
@@ -3489,11 +3552,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3505,11 +3568,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="15"/>
@@ -3627,6 +3690,18 @@
         <v>78</v>
       </c>
       <c r="CZ9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC9">
+        <v>90</v>
+      </c>
+      <c r="DD9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG9">
+        <v>90</v>
+      </c>
+      <c r="DH9" t="s">
         <v>141</v>
       </c>
       <c r="PS9" s="3">
@@ -3656,11 +3731,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>400</v>
+        <v>580</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
@@ -3676,11 +3751,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
@@ -3692,11 +3767,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="15"/>
@@ -3826,6 +3901,18 @@
         <v>90</v>
       </c>
       <c r="CZ10" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC10">
+        <v>90</v>
+      </c>
+      <c r="DD10" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG10">
+        <v>90</v>
+      </c>
+      <c r="DH10" t="s">
         <v>141</v>
       </c>
       <c r="PS10" s="3">
@@ -3855,11 +3942,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>310</v>
+        <v>480</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D11">
         <f t="shared" si="6"/>
@@ -3875,11 +3962,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -3891,11 +3978,11 @@
       </c>
       <c r="K11">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="15"/>
@@ -4023,6 +4110,18 @@
       </c>
       <c r="CZ11" t="s">
         <v>149</v>
+      </c>
+      <c r="DC11">
+        <v>80</v>
+      </c>
+      <c r="DD11" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG11">
+        <v>90</v>
+      </c>
+      <c r="DH11" t="s">
+        <v>141</v>
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
@@ -4199,13 +4298,19 @@
       <c r="CZ12" t="s">
         <v>142</v>
       </c>
+      <c r="DD12" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH12" t="s">
+        <v>149</v>
+      </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PT12" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PU12" s="3">
         <f t="shared" si="34"/>
@@ -4226,11 +4331,11 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
@@ -4246,7 +4351,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
@@ -4254,7 +4359,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="12"/>
@@ -4262,7 +4367,7 @@
       </c>
       <c r="K13">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="14"/>
@@ -4270,7 +4375,7 @@
       </c>
       <c r="M13" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="16"/>
@@ -4389,13 +4494,22 @@
       <c r="CZ13" t="s">
         <v>149</v>
       </c>
+      <c r="DD13" t="s">
+        <v>149</v>
+      </c>
+      <c r="DG13">
+        <v>23</v>
+      </c>
+      <c r="DH13" t="s">
+        <v>142</v>
+      </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="34"/>
@@ -4416,11 +4530,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>257</v>
+        <v>414</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
@@ -4436,11 +4550,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
@@ -4452,11 +4566,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="15"/>
@@ -4581,6 +4695,18 @@
       </c>
       <c r="CZ14" t="s">
         <v>142</v>
+      </c>
+      <c r="DC14">
+        <v>90</v>
+      </c>
+      <c r="DD14" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG14">
+        <v>67</v>
+      </c>
+      <c r="DH14" t="s">
+        <v>141</v>
       </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
@@ -4778,13 +4904,19 @@
       <c r="CZ15" t="s">
         <v>149</v>
       </c>
+      <c r="DD15" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH15" t="s">
+        <v>149</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
@@ -4953,13 +5085,19 @@
       <c r="CZ16" t="s">
         <v>149</v>
       </c>
+      <c r="DD16" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH16" t="s">
+        <v>149</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
@@ -4980,11 +5118,11 @@
       </c>
       <c r="B17">
         <f t="shared" si="36"/>
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <f t="shared" si="6"/>
@@ -5000,7 +5138,7 @@
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
@@ -5008,7 +5146,7 @@
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17" s="3">
         <f t="shared" si="12"/>
@@ -5016,7 +5154,7 @@
       </c>
       <c r="K17">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="14"/>
@@ -5024,7 +5162,7 @@
       </c>
       <c r="M17" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" s="3">
         <f t="shared" si="16"/>
@@ -5154,6 +5292,18 @@
       </c>
       <c r="DA17">
         <v>1</v>
+      </c>
+      <c r="DC17">
+        <v>17</v>
+      </c>
+      <c r="DD17" t="s">
+        <v>142</v>
+      </c>
+      <c r="DG17">
+        <v>23</v>
+      </c>
+      <c r="DH17" t="s">
+        <v>142</v>
       </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
@@ -5182,11 +5332,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>178</v>
+        <v>251</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
@@ -5202,15 +5352,15 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="12"/>
@@ -5218,15 +5368,15 @@
       </c>
       <c r="K18">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="16"/>
@@ -5266,11 +5416,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="50"/>
@@ -5282,7 +5432,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -5337,6 +5487,21 @@
         <v>28</v>
       </c>
       <c r="CZ18" t="s">
+        <v>142</v>
+      </c>
+      <c r="DC18">
+        <v>58</v>
+      </c>
+      <c r="DD18" t="s">
+        <v>141</v>
+      </c>
+      <c r="DE18">
+        <v>1</v>
+      </c>
+      <c r="DG18">
+        <v>15</v>
+      </c>
+      <c r="DH18" t="s">
         <v>142</v>
       </c>
       <c r="PS18" s="3">
@@ -5366,11 +5531,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>373</v>
+        <v>521</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
@@ -5386,11 +5551,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
@@ -5402,11 +5567,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="15"/>
@@ -5536,6 +5701,18 @@
         <v>78</v>
       </c>
       <c r="CZ19" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC19">
+        <v>73</v>
+      </c>
+      <c r="DD19" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG19">
+        <v>75</v>
+      </c>
+      <c r="DH19" t="s">
         <v>141</v>
       </c>
       <c r="PS19" s="3">
@@ -5728,13 +5905,19 @@
       <c r="CZ20" t="s">
         <v>149</v>
       </c>
+      <c r="DD20" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH20" t="s">
+        <v>149</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
@@ -5918,13 +6101,19 @@
       <c r="CZ21" t="s">
         <v>149</v>
       </c>
+      <c r="DD21" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH21" t="s">
+        <v>149</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
@@ -6117,13 +6306,19 @@
       <c r="CZ22" t="s">
         <v>149</v>
       </c>
+      <c r="DD22" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH22" t="s">
+        <v>149</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
@@ -6310,13 +6505,19 @@
       <c r="CZ23" t="s">
         <v>149</v>
       </c>
+      <c r="DD23" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH23" t="s">
+        <v>149</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT23" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU23" s="3">
         <f t="shared" si="34"/>
@@ -6337,11 +6538,11 @@
       </c>
       <c r="B24">
         <f t="shared" si="36"/>
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
@@ -6357,7 +6558,7 @@
       </c>
       <c r="G24">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="10"/>
@@ -6365,7 +6566,7 @@
       </c>
       <c r="I24" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <f t="shared" si="12"/>
@@ -6373,7 +6574,7 @@
       </c>
       <c r="K24">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="14"/>
@@ -6381,7 +6582,7 @@
       </c>
       <c r="M24" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="3">
         <f t="shared" si="16"/>
@@ -6506,13 +6707,22 @@
       <c r="DB24">
         <v>1</v>
       </c>
+      <c r="DC24">
+        <v>10</v>
+      </c>
+      <c r="DD24" t="s">
+        <v>142</v>
+      </c>
+      <c r="DH24" t="s">
+        <v>149</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="34"/>
@@ -6533,11 +6743,11 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>250</v>
+        <v>420</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
@@ -6553,11 +6763,11 @@
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -6569,11 +6779,11 @@
       </c>
       <c r="K25">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="3">
         <f t="shared" si="15"/>
@@ -6698,6 +6908,18 @@
       </c>
       <c r="CZ25" t="s">
         <v>149</v>
+      </c>
+      <c r="DC25">
+        <v>80</v>
+      </c>
+      <c r="DD25" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG25">
+        <v>90</v>
+      </c>
+      <c r="DH25" t="s">
+        <v>141</v>
       </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
@@ -6871,13 +7093,19 @@
       <c r="CZ26" t="s">
         <v>142</v>
       </c>
+      <c r="DD26" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH26" t="s">
+        <v>149</v>
+      </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="34"/>
@@ -7049,13 +7277,19 @@
       <c r="CZ27" t="s">
         <v>149</v>
       </c>
+      <c r="DD27" t="s">
+        <v>149</v>
+      </c>
+      <c r="DH27" t="s">
+        <v>149</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
@@ -7076,11 +7310,11 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>350</v>
+        <v>530</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
@@ -7096,11 +7330,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -7112,11 +7346,11 @@
       </c>
       <c r="K28">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="15"/>
@@ -7240,6 +7474,18 @@
         <v>90</v>
       </c>
       <c r="CZ28" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC28">
+        <v>90</v>
+      </c>
+      <c r="DD28" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG28">
+        <v>90</v>
+      </c>
+      <c r="DH28" t="s">
         <v>141</v>
       </c>
       <c r="PS28" s="3">
@@ -7269,11 +7515,11 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>375</v>
+        <v>540</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="D29">
         <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
@@ -7289,11 +7535,11 @@
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -7305,11 +7551,11 @@
       </c>
       <c r="K29">
         <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
@@ -7439,6 +7685,18 @@
         <v>90</v>
       </c>
       <c r="CZ29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC29">
+        <v>90</v>
+      </c>
+      <c r="DD29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DG29">
+        <v>75</v>
+      </c>
+      <c r="DH29" t="s">
         <v>141</v>
       </c>
       <c r="PS29" s="3">
@@ -7468,11 +7726,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -7488,15 +7746,15 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="98">COUNTIF(AI30:PR30,"NR")</f>
@@ -7504,15 +7762,15 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="3">
         <f t="shared" ref="N30" si="102">COUNTIF(CY30:GX30,"NR")</f>
@@ -7602,6 +7860,18 @@
         <v>75</v>
       </c>
       <c r="CZ30" t="s">
+        <v>141</v>
+      </c>
+      <c r="DC30">
+        <v>10</v>
+      </c>
+      <c r="DD30" t="s">
+        <v>142</v>
+      </c>
+      <c r="DG30">
+        <v>67</v>
+      </c>
+      <c r="DH30" t="s">
         <v>141</v>
       </c>
       <c r="PS30" s="3">
@@ -7631,11 +7901,11 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="120">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="121">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="122">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
@@ -7651,7 +7921,7 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="125">SUM(H31:I31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="126">COUNTIF(AI31:PR31,"T")</f>
@@ -7659,7 +7929,7 @@
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="127">COUNTIF(AI31:PR31,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="3">
         <f t="shared" ref="J31" si="128">COUNTIF(AI31:PR31,"NR")</f>
@@ -7667,7 +7937,7 @@
       </c>
       <c r="K31">
         <f t="shared" ref="K31" si="129">SUM(L31:M31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" ref="L31" si="130">COUNTIF(CY31:GX31,"T")</f>
@@ -7675,7 +7945,7 @@
       </c>
       <c r="M31" s="3">
         <f t="shared" ref="M31" si="131">COUNTIF(CY31:GX31,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="3">
         <f t="shared" ref="N31" si="132">COUNTIF(CY31:GX31,"NR")</f>
@@ -7764,13 +8034,22 @@
       <c r="CZ31" t="s">
         <v>149</v>
       </c>
+      <c r="DC31">
+        <v>32</v>
+      </c>
+      <c r="DD31" t="s">
+        <v>142</v>
+      </c>
+      <c r="DH31" t="s">
+        <v>149</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
@@ -7783,6 +8062,17 @@
       <c r="PW31">
         <f t="shared" ref="PW31" si="149">G31-(K31+O31+S31)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:439" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>150</v>
+      </c>
+      <c r="DG32">
+        <v>15</v>
+      </c>
+      <c r="DH32" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157E9603-4402-324E-8C81-02F95F3E108E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82978E1A-9169-B94C-8812-EF07DF20F0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="152">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2247,11 +2247,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2369,6 +2369,12 @@
         <v>90</v>
       </c>
       <c r="DH2" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK2">
+        <v>90</v>
+      </c>
+      <c r="DL2" t="s">
         <v>141</v>
       </c>
       <c r="PS2" s="3">
@@ -2543,13 +2549,16 @@
       <c r="DH3" t="s">
         <v>149</v>
       </c>
+      <c r="DL3" t="s">
+        <v>149</v>
+      </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT28" si="33">COUNTIF(CY3:GX3,"HG")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU28" si="34">COUNTIF(GY3:IT3,"HG")</f>
@@ -2733,13 +2742,16 @@
       <c r="DH4" t="s">
         <v>149</v>
       </c>
+      <c r="DL4" t="s">
+        <v>149</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
@@ -2792,7 +2804,7 @@
       </c>
       <c r="J5" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" si="13"/>
@@ -2808,7 +2820,7 @@
       </c>
       <c r="N5" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5">
         <f t="shared" si="17"/>
@@ -2931,6 +2943,9 @@
       </c>
       <c r="DH5" t="s">
         <v>141</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>151</v>
       </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
@@ -2959,11 +2974,11 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>259</v>
+        <v>341</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
@@ -2979,11 +2994,11 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
@@ -2995,11 +3010,11 @@
       </c>
       <c r="K6">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="15"/>
@@ -3139,6 +3154,12 @@
       </c>
       <c r="DH6" t="s">
         <v>151</v>
+      </c>
+      <c r="DK6">
+        <v>82</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>141</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
@@ -3312,13 +3333,16 @@
       <c r="DH7" t="s">
         <v>149</v>
       </c>
+      <c r="DL7" t="s">
+        <v>149</v>
+      </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
@@ -3505,13 +3529,16 @@
       <c r="DH8" t="s">
         <v>149</v>
       </c>
+      <c r="DL8" t="s">
+        <v>149</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="34"/>
@@ -3532,11 +3559,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>503</v>
+        <v>593</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
-        <v>258</v>
+        <v>348</v>
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
@@ -3552,11 +3579,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3568,11 +3595,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="15"/>
@@ -3702,6 +3729,12 @@
         <v>90</v>
       </c>
       <c r="DH9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK9">
+        <v>90</v>
+      </c>
+      <c r="DL9" t="s">
         <v>141</v>
       </c>
       <c r="PS9" s="3">
@@ -3731,11 +3764,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>580</v>
+        <v>670</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
@@ -3751,11 +3784,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
@@ -3767,11 +3800,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="15"/>
@@ -3913,6 +3946,12 @@
         <v>90</v>
       </c>
       <c r="DH10" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK10">
+        <v>90</v>
+      </c>
+      <c r="DL10" t="s">
         <v>141</v>
       </c>
       <c r="PS10" s="3">
@@ -3942,11 +3981,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>480</v>
+        <v>554</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
-        <v>170</v>
+        <v>244</v>
       </c>
       <c r="D11">
         <f t="shared" si="6"/>
@@ -3962,11 +4001,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -3978,11 +4017,11 @@
       </c>
       <c r="K11">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="15"/>
@@ -4026,11 +4065,11 @@
       </c>
       <c r="W11" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="50"/>
@@ -4042,7 +4081,7 @@
       </c>
       <c r="AA11">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11">
         <f t="shared" si="26"/>
@@ -4122,6 +4161,15 @@
       </c>
       <c r="DH11" t="s">
         <v>141</v>
+      </c>
+      <c r="DK11">
+        <v>74</v>
+      </c>
+      <c r="DL11" t="s">
+        <v>141</v>
+      </c>
+      <c r="DM11">
+        <v>1</v>
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
@@ -4304,13 +4352,16 @@
       <c r="DH12" t="s">
         <v>149</v>
       </c>
+      <c r="DL12" t="s">
+        <v>149</v>
+      </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT12" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU12" s="3">
         <f t="shared" si="34"/>
@@ -4331,11 +4382,11 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
@@ -4351,7 +4402,7 @@
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
@@ -4359,7 +4410,7 @@
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13" s="3">
         <f t="shared" si="12"/>
@@ -4367,7 +4418,7 @@
       </c>
       <c r="K13">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="14"/>
@@ -4375,7 +4426,7 @@
       </c>
       <c r="M13" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3">
         <f t="shared" si="16"/>
@@ -4501,6 +4552,12 @@
         <v>23</v>
       </c>
       <c r="DH13" t="s">
+        <v>142</v>
+      </c>
+      <c r="DK13">
+        <v>8</v>
+      </c>
+      <c r="DL13" t="s">
         <v>142</v>
       </c>
       <c r="PS13" s="3">
@@ -4530,11 +4587,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>414</v>
+        <v>483</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
@@ -4550,11 +4607,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
@@ -4566,11 +4623,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <f t="shared" si="15"/>
@@ -4706,6 +4763,12 @@
         <v>67</v>
       </c>
       <c r="DH14" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK14">
+        <v>69</v>
+      </c>
+      <c r="DL14" t="s">
         <v>141</v>
       </c>
       <c r="PS14" s="3">
@@ -4910,13 +4973,16 @@
       <c r="DH15" t="s">
         <v>149</v>
       </c>
+      <c r="DL15" t="s">
+        <v>149</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
@@ -5091,13 +5157,16 @@
       <c r="DH16" t="s">
         <v>149</v>
       </c>
+      <c r="DL16" t="s">
+        <v>149</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
@@ -5118,11 +5187,11 @@
       </c>
       <c r="B17">
         <f t="shared" si="36"/>
-        <v>380</v>
+        <v>446</v>
       </c>
       <c r="C17">
         <f t="shared" si="5"/>
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="D17">
         <f t="shared" si="6"/>
@@ -5138,11 +5207,11 @@
       </c>
       <c r="G17">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="11"/>
@@ -5154,11 +5223,11 @@
       </c>
       <c r="K17">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3">
         <f t="shared" si="15"/>
@@ -5304,6 +5373,12 @@
       </c>
       <c r="DH17" t="s">
         <v>142</v>
+      </c>
+      <c r="DK17">
+        <v>66</v>
+      </c>
+      <c r="DL17" t="s">
+        <v>141</v>
       </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
@@ -5332,11 +5407,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
@@ -5352,11 +5427,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
@@ -5368,11 +5443,11 @@
       </c>
       <c r="K18">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="15"/>
@@ -5424,11 +5499,11 @@
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
@@ -5436,7 +5511,7 @@
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18">
         <f t="shared" si="27"/>
@@ -5503,6 +5578,15 @@
       </c>
       <c r="DH18" t="s">
         <v>142</v>
+      </c>
+      <c r="DK18">
+        <v>82</v>
+      </c>
+      <c r="DL18" t="s">
+        <v>141</v>
+      </c>
+      <c r="DN18">
+        <v>1</v>
       </c>
       <c r="PS18" s="3">
         <f t="shared" si="32"/>
@@ -5531,11 +5615,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
@@ -5551,7 +5635,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
@@ -5559,7 +5643,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="12"/>
@@ -5567,7 +5651,7 @@
       </c>
       <c r="K19">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="14"/>
@@ -5575,7 +5659,7 @@
       </c>
       <c r="M19" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="3">
         <f t="shared" si="16"/>
@@ -5714,6 +5798,12 @@
       </c>
       <c r="DH19" t="s">
         <v>141</v>
+      </c>
+      <c r="DK19">
+        <v>21</v>
+      </c>
+      <c r="DL19" t="s">
+        <v>142</v>
       </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
@@ -5911,13 +6001,16 @@
       <c r="DH20" t="s">
         <v>149</v>
       </c>
+      <c r="DL20" t="s">
+        <v>149</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
@@ -6107,13 +6200,16 @@
       <c r="DH21" t="s">
         <v>149</v>
       </c>
+      <c r="DL21" t="s">
+        <v>149</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
@@ -6312,13 +6408,16 @@
       <c r="DH22" t="s">
         <v>149</v>
       </c>
+      <c r="DL22" t="s">
+        <v>149</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
@@ -6511,13 +6610,16 @@
       <c r="DH23" t="s">
         <v>149</v>
       </c>
+      <c r="DL23" t="s">
+        <v>149</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT23" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU23" s="3">
         <f t="shared" si="34"/>
@@ -6716,13 +6818,16 @@
       <c r="DH24" t="s">
         <v>149</v>
       </c>
+      <c r="DL24" t="s">
+        <v>149</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="34"/>
@@ -6743,11 +6848,11 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
@@ -6763,11 +6868,11 @@
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -6779,11 +6884,11 @@
       </c>
       <c r="K25">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M25" s="3">
         <f t="shared" si="15"/>
@@ -6919,6 +7024,12 @@
         <v>90</v>
       </c>
       <c r="DH25" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK25">
+        <v>90</v>
+      </c>
+      <c r="DL25" t="s">
         <v>141</v>
       </c>
       <c r="PS25" s="3">
@@ -6948,11 +7059,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="36"/>
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C26">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D26">
         <f t="shared" si="6"/>
@@ -6968,7 +7079,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="10"/>
@@ -6976,7 +7087,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="12"/>
@@ -6984,7 +7095,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="14"/>
@@ -6992,7 +7103,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="16"/>
@@ -7098,6 +7209,12 @@
       </c>
       <c r="DH26" t="s">
         <v>149</v>
+      </c>
+      <c r="DK26">
+        <v>8</v>
+      </c>
+      <c r="DL26" t="s">
+        <v>142</v>
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
@@ -7283,13 +7400,16 @@
       <c r="DH27" t="s">
         <v>149</v>
       </c>
+      <c r="DL27" t="s">
+        <v>149</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
@@ -7310,11 +7430,11 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
-        <v>270</v>
+        <v>360</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
@@ -7330,11 +7450,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -7346,11 +7466,11 @@
       </c>
       <c r="K28">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="15"/>
@@ -7486,6 +7606,12 @@
         <v>90</v>
       </c>
       <c r="DH28" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK28">
+        <v>90</v>
+      </c>
+      <c r="DL28" t="s">
         <v>141</v>
       </c>
       <c r="PS28" s="3">
@@ -7515,11 +7641,11 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>540</v>
+        <v>630</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
-        <v>255</v>
+        <v>345</v>
       </c>
       <c r="D29">
         <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
@@ -7535,11 +7661,11 @@
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -7551,11 +7677,11 @@
       </c>
       <c r="K29">
         <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
@@ -7697,6 +7823,12 @@
         <v>75</v>
       </c>
       <c r="DH29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DK29">
+        <v>90</v>
+      </c>
+      <c r="DL29" t="s">
         <v>141</v>
       </c>
       <c r="PS29" s="3">
@@ -7726,11 +7858,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -7746,7 +7878,7 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
@@ -7754,7 +7886,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="98">COUNTIF(AI30:PR30,"NR")</f>
@@ -7762,7 +7894,7 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
@@ -7770,7 +7902,7 @@
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30" s="3">
         <f t="shared" ref="N30" si="102">COUNTIF(CY30:GX30,"NR")</f>
@@ -7873,6 +8005,12 @@
       </c>
       <c r="DH30" t="s">
         <v>141</v>
+      </c>
+      <c r="DK30">
+        <v>16</v>
+      </c>
+      <c r="DL30" t="s">
+        <v>142</v>
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
@@ -8043,13 +8181,16 @@
       <c r="DH31" t="s">
         <v>149</v>
       </c>
+      <c r="DL31" t="s">
+        <v>149</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
@@ -8073,6 +8214,9 @@
       </c>
       <c r="DH32" t="s">
         <v>142</v>
+      </c>
+      <c r="DL32" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82978E1A-9169-B94C-8812-EF07DF20F0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913F61F1-904F-2841-8545-6FA7D10DE5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="153">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -492,6 +492,9 @@
   </si>
   <si>
     <t>NR</t>
+  </si>
+  <si>
+    <t>Glenn Manga-Tabi</t>
   </si>
 </sst>
 </file>
@@ -879,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F67B87-FE0E-FC4A-8FE6-DAAF2AFECC8B}">
-  <dimension ref="A1:PW32"/>
+  <dimension ref="A1:PW33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -2211,11 +2214,11 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
@@ -2231,11 +2234,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2247,11 +2250,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2375,6 +2378,18 @@
         <v>90</v>
       </c>
       <c r="DL2" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO2">
+        <v>90</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS2">
+        <v>90</v>
+      </c>
+      <c r="DT2" t="s">
         <v>141</v>
       </c>
       <c r="PS2" s="3">
@@ -2552,13 +2567,19 @@
       <c r="DL3" t="s">
         <v>149</v>
       </c>
+      <c r="DP3" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT3" t="s">
+        <v>149</v>
+      </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PT3" s="3">
         <f t="shared" ref="PT3:PT28" si="33">COUNTIF(CY3:GX3,"HG")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PU3" s="3">
         <f t="shared" ref="PU3:PU28" si="34">COUNTIF(GY3:IT3,"HG")</f>
@@ -2745,13 +2766,19 @@
       <c r="DL4" t="s">
         <v>149</v>
       </c>
+      <c r="DP4" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>149</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
@@ -2772,11 +2799,11 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D5">
         <f t="shared" si="6"/>
@@ -2792,7 +2819,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
@@ -2800,7 +2827,7 @@
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3">
         <f t="shared" si="12"/>
@@ -2808,7 +2835,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="3">
         <f t="shared" si="14"/>
@@ -2816,7 +2843,7 @@
       </c>
       <c r="M5" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3">
         <f t="shared" si="16"/>
@@ -2947,13 +2974,22 @@
       <c r="DL5" t="s">
         <v>151</v>
       </c>
+      <c r="DP5" t="s">
+        <v>149</v>
+      </c>
+      <c r="DS5">
+        <v>4</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>142</v>
+      </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT5" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU5" s="3">
         <f t="shared" si="34"/>
@@ -2974,11 +3010,11 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>341</v>
+        <v>521</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
@@ -2994,11 +3030,11 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
@@ -3010,11 +3046,11 @@
       </c>
       <c r="K6">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="14"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="15"/>
@@ -3159,6 +3195,18 @@
         <v>82</v>
       </c>
       <c r="DL6" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO6">
+        <v>90</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS6">
+        <v>90</v>
+      </c>
+      <c r="DT6" t="s">
         <v>141</v>
       </c>
       <c r="PS6" s="3">
@@ -3336,13 +3384,19 @@
       <c r="DL7" t="s">
         <v>149</v>
       </c>
+      <c r="DP7" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT7" t="s">
+        <v>149</v>
+      </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
@@ -3532,13 +3586,19 @@
       <c r="DL8" t="s">
         <v>149</v>
       </c>
+      <c r="DP8" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT8" t="s">
+        <v>149</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="33"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="34"/>
@@ -3559,11 +3619,11 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>593</v>
+        <v>773</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
-        <v>348</v>
+        <v>528</v>
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
@@ -3579,11 +3639,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3595,11 +3655,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="15"/>
@@ -3735,6 +3795,18 @@
         <v>90</v>
       </c>
       <c r="DL9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO9">
+        <v>90</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS9">
+        <v>90</v>
+      </c>
+      <c r="DT9" t="s">
         <v>141</v>
       </c>
       <c r="PS9" s="3">
@@ -3764,11 +3836,11 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>670</v>
+        <v>694</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
@@ -3784,7 +3856,7 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
@@ -3792,15 +3864,15 @@
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="14"/>
@@ -3808,11 +3880,11 @@
       </c>
       <c r="M10" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="3">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
         <f t="shared" si="17"/>
@@ -3953,6 +4025,15 @@
       </c>
       <c r="DL10" t="s">
         <v>141</v>
+      </c>
+      <c r="DP10" t="s">
+        <v>151</v>
+      </c>
+      <c r="DS10">
+        <v>24</v>
+      </c>
+      <c r="DT10" t="s">
+        <v>142</v>
       </c>
       <c r="PS10" s="3">
         <f t="shared" si="32"/>
@@ -3981,11 +4062,11 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
-        <v>244</v>
+        <v>424</v>
       </c>
       <c r="D11">
         <f t="shared" si="6"/>
@@ -4001,11 +4082,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -4017,11 +4098,11 @@
       </c>
       <c r="K11">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="15"/>
@@ -4170,6 +4251,18 @@
       </c>
       <c r="DM11">
         <v>1</v>
+      </c>
+      <c r="DO11">
+        <v>90</v>
+      </c>
+      <c r="DP11" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS11">
+        <v>90</v>
+      </c>
+      <c r="DT11" t="s">
+        <v>141</v>
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
@@ -4198,11 +4291,11 @@
       </c>
       <c r="B12">
         <f t="shared" si="36"/>
-        <v>103</v>
+        <v>279</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="D12">
         <f t="shared" si="6"/>
@@ -4218,11 +4311,11 @@
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
@@ -4234,11 +4327,11 @@
       </c>
       <c r="K12">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" s="3">
         <f t="shared" si="15"/>
@@ -4354,6 +4447,18 @@
       </c>
       <c r="DL12" t="s">
         <v>149</v>
+      </c>
+      <c r="DO12">
+        <v>90</v>
+      </c>
+      <c r="DP12" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS12">
+        <v>86</v>
+      </c>
+      <c r="DT12" t="s">
+        <v>141</v>
       </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
@@ -4382,11 +4487,11 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>241</v>
+        <v>361</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
@@ -4402,11 +4507,11 @@
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
@@ -4418,11 +4523,11 @@
       </c>
       <c r="K13">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="15"/>
@@ -4466,11 +4571,11 @@
       </c>
       <c r="W13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="50"/>
@@ -4482,7 +4587,7 @@
       </c>
       <c r="AA13">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13">
         <f t="shared" si="26"/>
@@ -4559,6 +4664,21 @@
       </c>
       <c r="DL13" t="s">
         <v>142</v>
+      </c>
+      <c r="DO13">
+        <v>75</v>
+      </c>
+      <c r="DP13" t="s">
+        <v>141</v>
+      </c>
+      <c r="DQ13">
+        <v>1</v>
+      </c>
+      <c r="DS13">
+        <v>45</v>
+      </c>
+      <c r="DT13" t="s">
+        <v>141</v>
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
@@ -4587,11 +4707,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>483</v>
+        <v>534</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
@@ -4607,7 +4727,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
@@ -4615,7 +4735,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="12"/>
@@ -4623,7 +4743,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="14"/>
@@ -4631,7 +4751,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="16"/>
@@ -4770,6 +4890,18 @@
       </c>
       <c r="DL14" t="s">
         <v>141</v>
+      </c>
+      <c r="DO14">
+        <v>6</v>
+      </c>
+      <c r="DP14" t="s">
+        <v>142</v>
+      </c>
+      <c r="DS14">
+        <v>45</v>
+      </c>
+      <c r="DT14" t="s">
+        <v>142</v>
       </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
@@ -4976,13 +5108,19 @@
       <c r="DL15" t="s">
         <v>149</v>
       </c>
+      <c r="DP15" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT15" t="s">
+        <v>149</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
@@ -5160,13 +5298,19 @@
       <c r="DL16" t="s">
         <v>149</v>
       </c>
+      <c r="DP16" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT16" t="s">
+        <v>149</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
@@ -5380,13 +5524,19 @@
       <c r="DL17" t="s">
         <v>141</v>
       </c>
+      <c r="DP17" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT17" t="s">
+        <v>149</v>
+      </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PT17" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PU17" s="3">
         <f t="shared" si="34"/>
@@ -5407,11 +5557,11 @@
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>333</v>
+        <v>429</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
-        <v>183</v>
+        <v>279</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
@@ -5427,15 +5577,15 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="12"/>
@@ -5443,15 +5593,15 @@
       </c>
       <c r="K18">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="3">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="16"/>
@@ -5491,11 +5641,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="50"/>
@@ -5507,7 +5657,7 @@
       </c>
       <c r="AA18">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB18">
         <f t="shared" si="26"/>
@@ -5587,6 +5737,21 @@
       </c>
       <c r="DN18">
         <v>1</v>
+      </c>
+      <c r="DO18">
+        <v>15</v>
+      </c>
+      <c r="DP18" t="s">
+        <v>142</v>
+      </c>
+      <c r="DQ18">
+        <v>1</v>
+      </c>
+      <c r="DS18">
+        <v>81</v>
+      </c>
+      <c r="DT18" t="s">
+        <v>141</v>
       </c>
       <c r="PS18" s="3">
         <f t="shared" si="32"/>
@@ -5615,11 +5780,11 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>542</v>
+        <v>632</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
-        <v>247</v>
+        <v>337</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
@@ -5635,11 +5800,11 @@
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
@@ -5651,11 +5816,11 @@
       </c>
       <c r="K19">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M19" s="3">
         <f t="shared" si="15"/>
@@ -5699,11 +5864,11 @@
       </c>
       <c r="W19" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="4">
         <f t="shared" si="50"/>
@@ -5715,7 +5880,7 @@
       </c>
       <c r="AA19">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
         <f t="shared" si="26"/>
@@ -5805,13 +5970,25 @@
       <c r="DL19" t="s">
         <v>142</v>
       </c>
+      <c r="DO19">
+        <v>90</v>
+      </c>
+      <c r="DP19" t="s">
+        <v>141</v>
+      </c>
+      <c r="DQ19">
+        <v>1</v>
+      </c>
+      <c r="DT19" t="s">
+        <v>149</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="34"/>
@@ -6004,13 +6181,19 @@
       <c r="DL20" t="s">
         <v>149</v>
       </c>
+      <c r="DP20" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT20" t="s">
+        <v>149</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
@@ -6203,13 +6386,19 @@
       <c r="DL21" t="s">
         <v>149</v>
       </c>
+      <c r="DP21" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT21" t="s">
+        <v>149</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
@@ -6411,13 +6600,19 @@
       <c r="DL22" t="s">
         <v>149</v>
       </c>
+      <c r="DP22" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT22" t="s">
+        <v>149</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
@@ -6613,13 +6808,19 @@
       <c r="DL23" t="s">
         <v>149</v>
       </c>
+      <c r="DP23" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT23" t="s">
+        <v>149</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT23" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU23" s="3">
         <f t="shared" si="34"/>
@@ -6821,13 +7022,19 @@
       <c r="DL24" t="s">
         <v>149</v>
       </c>
+      <c r="DP24" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT24" t="s">
+        <v>149</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="34"/>
@@ -6848,11 +7055,11 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>510</v>
+        <v>684</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
-        <v>260</v>
+        <v>434</v>
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
@@ -6868,11 +7075,11 @@
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -6884,11 +7091,11 @@
       </c>
       <c r="K25">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M25" s="3">
         <f t="shared" si="15"/>
@@ -7030,6 +7237,18 @@
         <v>90</v>
       </c>
       <c r="DL25" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO25">
+        <v>84</v>
+      </c>
+      <c r="DP25" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS25">
+        <v>90</v>
+      </c>
+      <c r="DT25" t="s">
         <v>141</v>
       </c>
       <c r="PS25" s="3">
@@ -7059,11 +7278,11 @@
       </c>
       <c r="B26">
         <f t="shared" si="36"/>
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <f t="shared" si="6"/>
@@ -7079,7 +7298,7 @@
       </c>
       <c r="G26">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="10"/>
@@ -7087,7 +7306,7 @@
       </c>
       <c r="I26" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J26" s="3">
         <f t="shared" si="12"/>
@@ -7095,7 +7314,7 @@
       </c>
       <c r="K26">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="14"/>
@@ -7103,7 +7322,7 @@
       </c>
       <c r="M26" s="3">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N26" s="3">
         <f t="shared" si="16"/>
@@ -7214,6 +7433,18 @@
         <v>8</v>
       </c>
       <c r="DL26" t="s">
+        <v>142</v>
+      </c>
+      <c r="DO26">
+        <v>18</v>
+      </c>
+      <c r="DP26" t="s">
+        <v>142</v>
+      </c>
+      <c r="DS26">
+        <v>9</v>
+      </c>
+      <c r="DT26" t="s">
         <v>142</v>
       </c>
       <c r="PS26" s="3">
@@ -7403,13 +7634,19 @@
       <c r="DL27" t="s">
         <v>149</v>
       </c>
+      <c r="DP27" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT27" t="s">
+        <v>149</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
@@ -7430,11 +7667,11 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>620</v>
+        <v>770</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
@@ -7450,11 +7687,11 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
@@ -7466,11 +7703,11 @@
       </c>
       <c r="K28">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="15"/>
@@ -7612,6 +7849,18 @@
         <v>90</v>
       </c>
       <c r="DL28" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO28">
+        <v>84</v>
+      </c>
+      <c r="DP28" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS28">
+        <v>66</v>
+      </c>
+      <c r="DT28" t="s">
         <v>141</v>
       </c>
       <c r="PS28" s="3">
@@ -7641,11 +7890,11 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>630</v>
+        <v>810</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
-        <v>345</v>
+        <v>525</v>
       </c>
       <c r="D29">
         <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
@@ -7661,11 +7910,11 @@
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -7677,11 +7926,11 @@
       </c>
       <c r="K29">
         <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
@@ -7829,6 +8078,18 @@
         <v>90</v>
       </c>
       <c r="DL29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DO29">
+        <v>90</v>
+      </c>
+      <c r="DP29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS29">
+        <v>90</v>
+      </c>
+      <c r="DT29" t="s">
         <v>141</v>
       </c>
       <c r="PS29" s="3">
@@ -7858,11 +8119,11 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
@@ -7878,11 +8139,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
@@ -7894,11 +8155,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
@@ -8011,6 +8272,18 @@
       </c>
       <c r="DL30" t="s">
         <v>142</v>
+      </c>
+      <c r="DO30">
+        <v>72</v>
+      </c>
+      <c r="DP30" t="s">
+        <v>141</v>
+      </c>
+      <c r="DS30">
+        <v>66</v>
+      </c>
+      <c r="DT30" t="s">
+        <v>141</v>
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
@@ -8184,13 +8457,19 @@
       <c r="DL31" t="s">
         <v>149</v>
       </c>
+      <c r="DP31" t="s">
+        <v>149</v>
+      </c>
+      <c r="DT31" t="s">
+        <v>149</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
@@ -8217,6 +8496,23 @@
       </c>
       <c r="DL32" t="s">
         <v>149</v>
+      </c>
+      <c r="DO32">
+        <v>6</v>
+      </c>
+      <c r="DP32" t="s">
+        <v>142</v>
+      </c>
+      <c r="DS32">
+        <v>24</v>
+      </c>
+      <c r="DT32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913F61F1-904F-2841-8545-6FA7D10DE5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774B33F5-5BBF-844F-8674-DC961F212F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="153">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>600</v>
+        <v>690</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <f>SUM(IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
@@ -2234,11 +2234,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="J2" s="3">
         <f>COUNTIF(AI2:PR2,"NR")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
@@ -2266,11 +2266,11 @@
       </c>
       <c r="O2">
         <f>SUM(P2:Q2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="3">
         <f>COUNTIF(GY2:IT2,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="3">
         <f>COUNTIF(GY2:IT2,"R")</f>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="R2" s="3">
         <f>COUNTIF(GY2:IT2,"NR")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2">
         <f>SUM(T2:U2)</f>
@@ -2390,6 +2390,15 @@
         <v>90</v>
       </c>
       <c r="DT2" t="s">
+        <v>141</v>
+      </c>
+      <c r="HD2" t="s">
+        <v>151</v>
+      </c>
+      <c r="HG2">
+        <v>90</v>
+      </c>
+      <c r="HH2" t="s">
         <v>141</v>
       </c>
       <c r="PS2" s="3">
@@ -2419,7 +2428,7 @@
       </c>
       <c r="B3">
         <f>SUM(AI3,AM3,AQ3,AU3,AY3,BC3,BG3,BK3,BO3,BS3,BW3,CA3,CE3,CI3,CM3,CQ3,CU3,CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3,GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3,IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C28" si="5">SUM(CY3,DC3,DG3,DK3,DO3,DS3,DW3,EA3,EE3,EI3,EM3,EQ3,EU3,EY3,FC3,FG3,FK3,FO3,FS3,FW3,GA3,GE3,GI3,GM3,GQ3,GU3)</f>
@@ -2427,7 +2436,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D28" si="6">SUM(GY3,HC3,HG3,HK3,HO3,HS3,HW3,IA3,IE3,II3,IM3,IQ3)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E28" si="7">SUM(IU3,IY3,JC3,JG3,JK3,JO3,JS3,JW3,KA3,KE3,KI3,KM3,KQ3,KU3,KY3,LC3,LG3,LK3,LO3,LS3,LW3,MA3,ME3,MI3,MM3,MQ3,MU3,MY3,NC3,NG3,NK3,NO3,NS3,NW3,OA3,OE3,OI3,OM3,OQ3,OU3,OY3,PC3,PG3,PK3,PO3)</f>
@@ -2439,11 +2448,11 @@
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G28" si="9">SUM(H3:I3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H28" si="10">COUNTIF(AI3:PR3,"T")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3">
         <f t="shared" ref="I3:I28" si="11">COUNTIF(AI3:PR3,"R")</f>
@@ -2451,7 +2460,7 @@
       </c>
       <c r="J3" s="3">
         <f t="shared" ref="J3:J28" si="12">COUNTIF(AI3:PR3,"NR")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:K28" si="13">SUM(L3:M3)</f>
@@ -2471,11 +2480,11 @@
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O28" si="17">SUM(P3:Q3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="3">
         <f t="shared" ref="P3:P28" si="18">COUNTIF(GY3:IT3,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="3">
         <f t="shared" ref="Q3:Q28" si="19">COUNTIF(GY3:IT3,"R")</f>
@@ -2483,7 +2492,7 @@
       </c>
       <c r="R3" s="3">
         <f t="shared" ref="R3:R28" si="20">COUNTIF(GY3:IT3,"NR")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S28" si="21">SUM(T3:U3)</f>
@@ -2572,6 +2581,15 @@
       </c>
       <c r="DT3" t="s">
         <v>149</v>
+      </c>
+      <c r="HC3">
+        <v>90</v>
+      </c>
+      <c r="HD3" t="s">
+        <v>141</v>
+      </c>
+      <c r="HH3" t="s">
+        <v>151</v>
       </c>
       <c r="PS3" s="3">
         <f t="shared" ref="PS3:PS28" si="32">COUNTIF(AI3:PR3,"HG")</f>
@@ -2772,9 +2790,15 @@
       <c r="DT4" t="s">
         <v>149</v>
       </c>
+      <c r="HD4" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH4" t="s">
+        <v>149</v>
+      </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
@@ -2782,7 +2806,7 @@
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV4">
         <f t="shared" si="4"/>
@@ -2799,7 +2823,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>527</v>
+        <v>707</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
@@ -2807,7 +2831,7 @@
       </c>
       <c r="D5">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E5">
         <f t="shared" si="7"/>
@@ -2819,11 +2843,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2851,11 +2875,11 @@
       </c>
       <c r="O5">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="19"/>
@@ -2982,6 +3006,18 @@
       </c>
       <c r="DT5" t="s">
         <v>142</v>
+      </c>
+      <c r="HC5">
+        <v>90</v>
+      </c>
+      <c r="HD5" t="s">
+        <v>141</v>
+      </c>
+      <c r="HG5">
+        <v>90</v>
+      </c>
+      <c r="HH5" t="s">
+        <v>141</v>
       </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
@@ -3010,7 +3046,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>521</v>
+        <v>619</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
@@ -3018,7 +3054,7 @@
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E6">
         <f t="shared" si="7"/>
@@ -3030,15 +3066,15 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" s="3">
         <f t="shared" si="12"/>
@@ -3062,15 +3098,15 @@
       </c>
       <c r="O6">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="3">
         <f t="shared" si="20"/>
@@ -3208,6 +3244,18 @@
       </c>
       <c r="DT6" t="s">
         <v>141</v>
+      </c>
+      <c r="HC6">
+        <v>90</v>
+      </c>
+      <c r="HD6" t="s">
+        <v>141</v>
+      </c>
+      <c r="HG6">
+        <v>8</v>
+      </c>
+      <c r="HH6" t="s">
+        <v>142</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
@@ -3390,9 +3438,15 @@
       <c r="DT7" t="s">
         <v>149</v>
       </c>
+      <c r="HD7" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH7" t="s">
+        <v>149</v>
+      </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
@@ -3400,7 +3454,7 @@
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV7">
         <f t="shared" si="4"/>
@@ -3592,9 +3646,15 @@
       <c r="DT8" t="s">
         <v>149</v>
       </c>
+      <c r="HD8" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH8" t="s">
+        <v>149</v>
+      </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="33"/>
@@ -3602,7 +3662,7 @@
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV8">
         <f t="shared" si="4"/>
@@ -3619,7 +3679,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>773</v>
+        <v>863</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
@@ -3627,7 +3687,7 @@
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E9">
         <f t="shared" si="7"/>
@@ -3639,11 +3699,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3671,11 +3731,11 @@
       </c>
       <c r="O9">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="19"/>
@@ -3809,9 +3869,18 @@
       <c r="DT9" t="s">
         <v>141</v>
       </c>
+      <c r="HD9" t="s">
+        <v>149</v>
+      </c>
+      <c r="HG9">
+        <v>90</v>
+      </c>
+      <c r="HH9" t="s">
+        <v>141</v>
+      </c>
       <c r="PS9" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT9" s="3">
         <f t="shared" si="33"/>
@@ -3819,7 +3888,7 @@
       </c>
       <c r="PU9" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV9">
         <f t="shared" si="4"/>
@@ -3836,7 +3905,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>694</v>
+        <v>806</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
@@ -3844,7 +3913,7 @@
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="E10">
         <f t="shared" si="7"/>
@@ -3856,15 +3925,15 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="3">
         <f t="shared" si="12"/>
@@ -3888,15 +3957,15 @@
       </c>
       <c r="O10">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="3">
         <f t="shared" si="20"/>
@@ -4033,6 +4102,18 @@
         <v>24</v>
       </c>
       <c r="DT10" t="s">
+        <v>142</v>
+      </c>
+      <c r="HC10">
+        <v>90</v>
+      </c>
+      <c r="HD10" t="s">
+        <v>141</v>
+      </c>
+      <c r="HG10">
+        <v>22</v>
+      </c>
+      <c r="HH10" t="s">
         <v>142</v>
       </c>
       <c r="PS10" s="3">
@@ -4062,7 +4143,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>734</v>
+        <v>914</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
@@ -4070,7 +4151,7 @@
       </c>
       <c r="D11">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E11">
         <f t="shared" si="7"/>
@@ -4082,11 +4163,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -4114,11 +4195,11 @@
       </c>
       <c r="O11">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P11" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="19"/>
@@ -4146,11 +4227,11 @@
       </c>
       <c r="W11" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X11" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="50"/>
@@ -4170,7 +4251,7 @@
       </c>
       <c r="AC11">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11">
         <f t="shared" si="28"/>
@@ -4263,6 +4344,24 @@
       </c>
       <c r="DT11" t="s">
         <v>141</v>
+      </c>
+      <c r="HC11">
+        <v>90</v>
+      </c>
+      <c r="HD11" t="s">
+        <v>141</v>
+      </c>
+      <c r="HE11">
+        <v>1</v>
+      </c>
+      <c r="HG11">
+        <v>90</v>
+      </c>
+      <c r="HH11" t="s">
+        <v>141</v>
+      </c>
+      <c r="HI11">
+        <v>1</v>
       </c>
       <c r="PS11" s="3">
         <f t="shared" si="32"/>
@@ -4291,7 +4390,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="36"/>
-        <v>279</v>
+        <v>448</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
@@ -4299,7 +4398,7 @@
       </c>
       <c r="D12">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="E12">
         <f t="shared" si="7"/>
@@ -4311,11 +4410,11 @@
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
@@ -4343,11 +4442,11 @@
       </c>
       <c r="O12">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" si="19"/>
@@ -4458,6 +4557,18 @@
         <v>86</v>
       </c>
       <c r="DT12" t="s">
+        <v>141</v>
+      </c>
+      <c r="HC12">
+        <v>79</v>
+      </c>
+      <c r="HD12" t="s">
+        <v>141</v>
+      </c>
+      <c r="HG12">
+        <v>90</v>
+      </c>
+      <c r="HH12" t="s">
         <v>141</v>
       </c>
       <c r="PS12" s="3">
@@ -4487,7 +4598,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>361</v>
+        <v>451</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
@@ -4495,7 +4606,7 @@
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E13">
         <f t="shared" si="7"/>
@@ -4507,11 +4618,11 @@
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
@@ -4539,11 +4650,11 @@
       </c>
       <c r="O13">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="3">
         <f t="shared" si="19"/>
@@ -4680,9 +4791,18 @@
       <c r="DT13" t="s">
         <v>141</v>
       </c>
+      <c r="HC13">
+        <v>90</v>
+      </c>
+      <c r="HD13" t="s">
+        <v>141</v>
+      </c>
+      <c r="HH13" t="s">
+        <v>149</v>
+      </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PT13" s="3">
         <f t="shared" si="33"/>
@@ -4690,7 +4810,7 @@
       </c>
       <c r="PU13" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV13">
         <f t="shared" si="4"/>
@@ -4707,7 +4827,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>534</v>
+        <v>699</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
@@ -4715,7 +4835,7 @@
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="E14">
         <f t="shared" si="7"/>
@@ -4727,11 +4847,11 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
@@ -4759,11 +4879,11 @@
       </c>
       <c r="O14">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P14" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="3">
         <f t="shared" si="19"/>
@@ -4902,6 +5022,18 @@
       </c>
       <c r="DT14" t="s">
         <v>142</v>
+      </c>
+      <c r="HC14">
+        <v>75</v>
+      </c>
+      <c r="HD14" t="s">
+        <v>141</v>
+      </c>
+      <c r="HG14">
+        <v>90</v>
+      </c>
+      <c r="HH14" t="s">
+        <v>141</v>
       </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
@@ -5114,9 +5246,15 @@
       <c r="DT15" t="s">
         <v>149</v>
       </c>
+      <c r="HD15" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH15" t="s">
+        <v>149</v>
+      </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
@@ -5124,7 +5262,7 @@
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV15">
         <f t="shared" si="4"/>
@@ -5141,7 +5279,7 @@
       </c>
       <c r="B16">
         <f t="shared" si="36"/>
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <f t="shared" si="5"/>
@@ -5149,7 +5287,7 @@
       </c>
       <c r="D16">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <f t="shared" si="7"/>
@@ -5161,7 +5299,7 @@
       </c>
       <c r="G16">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="10"/>
@@ -5169,7 +5307,7 @@
       </c>
       <c r="I16" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3">
         <f t="shared" si="12"/>
@@ -5193,7 +5331,7 @@
       </c>
       <c r="O16">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="3">
         <f t="shared" si="18"/>
@@ -5201,7 +5339,7 @@
       </c>
       <c r="Q16" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="3">
         <f t="shared" si="20"/>
@@ -5304,9 +5442,18 @@
       <c r="DT16" t="s">
         <v>149</v>
       </c>
+      <c r="HD16" t="s">
+        <v>149</v>
+      </c>
+      <c r="HG16">
+        <v>11</v>
+      </c>
+      <c r="HH16" t="s">
+        <v>142</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
@@ -5314,7 +5461,7 @@
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV16">
         <f t="shared" si="4"/>
@@ -5530,9 +5677,15 @@
       <c r="DT17" t="s">
         <v>149</v>
       </c>
+      <c r="HD17" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH17" t="s">
+        <v>149</v>
+      </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PT17" s="3">
         <f t="shared" si="33"/>
@@ -5540,7 +5693,7 @@
       </c>
       <c r="PU17" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV17">
         <f t="shared" si="4"/>
@@ -5557,7 +5710,7 @@
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>429</v>
+        <v>602</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
@@ -5565,7 +5718,7 @@
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="E18">
         <f t="shared" si="7"/>
@@ -5577,11 +5730,11 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
@@ -5609,11 +5762,11 @@
       </c>
       <c r="O18">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="3">
         <f t="shared" si="19"/>
@@ -5641,11 +5794,11 @@
       </c>
       <c r="W18" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X18" s="4">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y18" s="4">
         <f t="shared" si="50"/>
@@ -5665,7 +5818,7 @@
       </c>
       <c r="AC18">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18">
         <f t="shared" si="28"/>
@@ -5751,6 +5904,21 @@
         <v>81</v>
       </c>
       <c r="DT18" t="s">
+        <v>141</v>
+      </c>
+      <c r="HC18">
+        <v>83</v>
+      </c>
+      <c r="HD18" t="s">
+        <v>141</v>
+      </c>
+      <c r="HE18">
+        <v>2</v>
+      </c>
+      <c r="HG18">
+        <v>90</v>
+      </c>
+      <c r="HH18" t="s">
         <v>141</v>
       </c>
       <c r="PS18" s="3">
@@ -5780,7 +5948,7 @@
       </c>
       <c r="B19">
         <f t="shared" si="36"/>
-        <v>632</v>
+        <v>647</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
@@ -5788,7 +5956,7 @@
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E19">
         <f t="shared" si="7"/>
@@ -5800,7 +5968,7 @@
       </c>
       <c r="G19">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="10"/>
@@ -5808,7 +5976,7 @@
       </c>
       <c r="I19" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="3">
         <f t="shared" si="12"/>
@@ -5832,7 +6000,7 @@
       </c>
       <c r="O19">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="3">
         <f t="shared" si="18"/>
@@ -5840,7 +6008,7 @@
       </c>
       <c r="Q19" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="3">
         <f t="shared" si="20"/>
@@ -5982,9 +6150,18 @@
       <c r="DT19" t="s">
         <v>149</v>
       </c>
+      <c r="HC19">
+        <v>15</v>
+      </c>
+      <c r="HD19" t="s">
+        <v>142</v>
+      </c>
+      <c r="HH19" t="s">
+        <v>149</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="33"/>
@@ -5992,7 +6169,7 @@
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV19">
         <f t="shared" si="4"/>
@@ -6187,9 +6364,15 @@
       <c r="DT20" t="s">
         <v>149</v>
       </c>
+      <c r="HD20" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH20" t="s">
+        <v>149</v>
+      </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
@@ -6197,7 +6380,7 @@
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV20">
         <f t="shared" si="4"/>
@@ -6214,7 +6397,7 @@
       </c>
       <c r="B21">
         <f t="shared" si="36"/>
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C21">
         <f t="shared" si="5"/>
@@ -6222,7 +6405,7 @@
       </c>
       <c r="D21">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <f t="shared" si="7"/>
@@ -6234,7 +6417,7 @@
       </c>
       <c r="G21">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="10"/>
@@ -6242,7 +6425,7 @@
       </c>
       <c r="I21" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="3">
         <f t="shared" si="12"/>
@@ -6266,7 +6449,7 @@
       </c>
       <c r="O21">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="3">
         <f t="shared" si="18"/>
@@ -6274,7 +6457,7 @@
       </c>
       <c r="Q21" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="3">
         <f t="shared" si="20"/>
@@ -6392,9 +6575,18 @@
       <c r="DT21" t="s">
         <v>149</v>
       </c>
+      <c r="HC21">
+        <v>7</v>
+      </c>
+      <c r="HD21" t="s">
+        <v>142</v>
+      </c>
+      <c r="HH21" t="s">
+        <v>149</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
@@ -6402,7 +6594,7 @@
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV21">
         <f t="shared" si="4"/>
@@ -6606,9 +6798,15 @@
       <c r="DT22" t="s">
         <v>149</v>
       </c>
+      <c r="HD22" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH22" t="s">
+        <v>149</v>
+      </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
@@ -6616,7 +6814,7 @@
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV22">
         <f t="shared" si="4"/>
@@ -6814,9 +7012,15 @@
       <c r="DT23" t="s">
         <v>149</v>
       </c>
+      <c r="HD23" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH23" t="s">
+        <v>149</v>
+      </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT23" s="3">
         <f t="shared" si="33"/>
@@ -6824,7 +7028,7 @@
       </c>
       <c r="PU23" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV23">
         <f t="shared" si="4"/>
@@ -7028,9 +7232,15 @@
       <c r="DT24" t="s">
         <v>149</v>
       </c>
+      <c r="HD24" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH24" t="s">
+        <v>149</v>
+      </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="33"/>
@@ -7038,7 +7248,7 @@
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV24">
         <f t="shared" si="4"/>
@@ -7055,7 +7265,7 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>684</v>
+        <v>782</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
@@ -7063,7 +7273,7 @@
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <f t="shared" si="7"/>
@@ -7075,15 +7285,15 @@
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" s="3">
         <f t="shared" si="12"/>
@@ -7107,15 +7317,15 @@
       </c>
       <c r="O25">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="3">
         <f t="shared" si="20"/>
@@ -7139,11 +7349,11 @@
       </c>
       <c r="W25" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="50"/>
@@ -7163,7 +7373,7 @@
       </c>
       <c r="AC25">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25">
         <f t="shared" si="28"/>
@@ -7250,6 +7460,21 @@
       </c>
       <c r="DT25" t="s">
         <v>141</v>
+      </c>
+      <c r="HC25">
+        <v>90</v>
+      </c>
+      <c r="HD25" t="s">
+        <v>141</v>
+      </c>
+      <c r="HE25">
+        <v>1</v>
+      </c>
+      <c r="HG25">
+        <v>8</v>
+      </c>
+      <c r="HH25" t="s">
+        <v>142</v>
       </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
@@ -7278,7 +7503,7 @@
       </c>
       <c r="B26">
         <f t="shared" si="36"/>
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="C26">
         <f t="shared" si="5"/>
@@ -7286,7 +7511,7 @@
       </c>
       <c r="D26">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="E26">
         <f t="shared" si="7"/>
@@ -7298,11 +7523,11 @@
       </c>
       <c r="G26">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="3">
         <f t="shared" si="11"/>
@@ -7330,11 +7555,11 @@
       </c>
       <c r="O26">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="3">
         <f t="shared" si="19"/>
@@ -7362,11 +7587,11 @@
       </c>
       <c r="W26" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X26" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="4">
         <f t="shared" si="50"/>
@@ -7386,7 +7611,7 @@
       </c>
       <c r="AC26">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD26">
         <f t="shared" si="28"/>
@@ -7446,6 +7671,21 @@
       </c>
       <c r="DT26" t="s">
         <v>142</v>
+      </c>
+      <c r="HC26">
+        <v>75</v>
+      </c>
+      <c r="HD26" t="s">
+        <v>141</v>
+      </c>
+      <c r="HE26">
+        <v>1</v>
+      </c>
+      <c r="HG26">
+        <v>68</v>
+      </c>
+      <c r="HH26" t="s">
+        <v>141</v>
       </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
@@ -7640,9 +7880,15 @@
       <c r="DT27" t="s">
         <v>149</v>
       </c>
+      <c r="HD27" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH27" t="s">
+        <v>149</v>
+      </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
@@ -7650,7 +7896,7 @@
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV27">
         <f t="shared" si="4"/>
@@ -7667,7 +7913,7 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>770</v>
+        <v>867</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
@@ -7675,7 +7921,7 @@
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="E28">
         <f t="shared" si="7"/>
@@ -7687,15 +7933,15 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="12"/>
@@ -7719,15 +7965,15 @@
       </c>
       <c r="O28">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="3">
         <f t="shared" si="20"/>
@@ -7861,6 +8107,18 @@
         <v>66</v>
       </c>
       <c r="DT28" t="s">
+        <v>141</v>
+      </c>
+      <c r="HC28">
+        <v>15</v>
+      </c>
+      <c r="HD28" t="s">
+        <v>142</v>
+      </c>
+      <c r="HG28">
+        <v>82</v>
+      </c>
+      <c r="HH28" t="s">
         <v>141</v>
       </c>
       <c r="PS28" s="3">
@@ -8092,9 +8350,15 @@
       <c r="DT29" t="s">
         <v>141</v>
       </c>
+      <c r="HD29" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH29" t="s">
+        <v>149</v>
+      </c>
       <c r="PS29" s="3">
         <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PT29" s="3">
         <f t="shared" ref="PT29" si="87">COUNTIF(CY29:GX29,"HG")</f>
@@ -8102,7 +8366,7 @@
       </c>
       <c r="PU29" s="3">
         <f t="shared" ref="PU29" si="88">COUNTIF(GY29:IT29,"HG")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="PV29">
         <f t="shared" si="4"/>
@@ -8119,7 +8383,7 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
@@ -8127,7 +8391,7 @@
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E30">
         <f t="shared" ref="E30" si="93">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
@@ -8139,7 +8403,7 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
@@ -8147,7 +8411,7 @@
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="3">
         <f t="shared" ref="J30" si="98">COUNTIF(AI30:PR30,"NR")</f>
@@ -8171,7 +8435,7 @@
       </c>
       <c r="O30">
         <f t="shared" ref="O30" si="103">SUM(P30:Q30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="3">
         <f t="shared" ref="P30" si="104">COUNTIF(GY30:IT30,"T")</f>
@@ -8179,7 +8443,7 @@
       </c>
       <c r="Q30" s="3">
         <f t="shared" ref="Q30" si="105">COUNTIF(GY30:IT30,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="3">
         <f t="shared" ref="R30" si="106">COUNTIF(GY30:IT30,"NR")</f>
@@ -8285,9 +8549,18 @@
       <c r="DT30" t="s">
         <v>141</v>
       </c>
+      <c r="HC30">
+        <v>11</v>
+      </c>
+      <c r="HD30" t="s">
+        <v>142</v>
+      </c>
+      <c r="HH30" t="s">
+        <v>149</v>
+      </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT30" s="3">
         <f t="shared" ref="PT30" si="117">COUNTIF(CY30:GX30,"HG")</f>
@@ -8295,7 +8568,7 @@
       </c>
       <c r="PU30" s="3">
         <f t="shared" ref="PU30" si="118">COUNTIF(GY30:IT30,"HG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV30">
         <f t="shared" si="4"/>
@@ -8363,19 +8636,19 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <f t="shared" ref="O31" si="133">SUM(P31:Q31)</f>
+        <f t="shared" ref="O31:O33" si="133">SUM(P31:Q31)</f>
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <f t="shared" ref="P31" si="134">COUNTIF(GY31:IT31,"T")</f>
+        <f t="shared" ref="P31:P33" si="134">COUNTIF(GY31:IT31,"T")</f>
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <f t="shared" ref="Q31" si="135">COUNTIF(GY31:IT31,"R")</f>
+        <f t="shared" ref="Q31:Q33" si="135">COUNTIF(GY31:IT31,"R")</f>
         <v>0</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" ref="R31" si="136">COUNTIF(GY31:IT31,"NR")</f>
+        <f t="shared" ref="R31:R33" si="136">COUNTIF(GY31:IT31,"NR")</f>
         <v>0</v>
       </c>
       <c r="S31">
@@ -8463,17 +8736,23 @@
       <c r="DT31" t="s">
         <v>149</v>
       </c>
+      <c r="HD31" t="s">
+        <v>149</v>
+      </c>
+      <c r="HH31" t="s">
+        <v>149</v>
+      </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
         <v>5</v>
       </c>
       <c r="PU31" s="3">
-        <f t="shared" ref="PU31" si="148">COUNTIF(GY31:IT31,"HG")</f>
-        <v>0</v>
+        <f t="shared" ref="PU31:PU33" si="148">COUNTIF(GY31:IT31,"HG")</f>
+        <v>2</v>
       </c>
       <c r="PV31">
         <f t="shared" si="4"/>
@@ -8488,6 +8767,22 @@
       <c r="A32" t="s">
         <v>150</v>
       </c>
+      <c r="O32">
+        <f t="shared" si="133"/>
+        <v>1</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="134"/>
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
       <c r="DG32">
         <v>15</v>
       </c>
@@ -8509,10 +8804,55 @@
       <c r="DT32" t="s">
         <v>142</v>
       </c>
+      <c r="HD32" t="s">
+        <v>149</v>
+      </c>
+      <c r="HG32">
+        <v>79</v>
+      </c>
+      <c r="HH32" t="s">
+        <v>141</v>
+      </c>
+      <c r="PU32">
+        <f t="shared" si="148"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:437" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>152</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="133"/>
+        <v>1</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="134"/>
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="135"/>
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="136"/>
+        <v>0</v>
+      </c>
+      <c r="HD33" t="s">
+        <v>149</v>
+      </c>
+      <c r="HG33">
+        <v>82</v>
+      </c>
+      <c r="HH33" t="s">
+        <v>141</v>
+      </c>
+      <c r="HI33">
+        <v>1</v>
+      </c>
+      <c r="PU33">
+        <f t="shared" si="148"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Temps de jeu.xlsx
+++ b/data/2026-2027/Temps de jeu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774B33F5-5BBF-844F-8674-DC961F212F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2841B8-5F71-7E4C-8909-1B445F4160ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{4D7058D9-FEBF-074A-9E43-9512510F2605}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="153">
   <si>
     <t xml:space="preserve">Match Amical 2 </t>
   </si>
@@ -2214,15 +2214,15 @@
       </c>
       <c r="B2">
         <f>SUM(AI2,AM2,AQ2,AU2,AY2,BC2,BG2,BK2,BO2,BS2,BW2,CA2,CE2,CI2,CM2,CQ2,CU2,CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2,GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2,IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="C2">
         <f>SUM(CY2,DC2,DG2,DK2,DO2,DS2,DW2,EA2,EE2,EI2,EM2,EQ2,EU2,EY2,FC2,FG2,FK2,FO2,FS2,FW2,GA2,GE2,GI2,GM2,GQ2,GU2)</f>
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="D2">
         <f>SUM(GY2,HC2,HG2,HK2,HO2,HS2,HW2,IA2,IE2,II2,IM2,IQ2)</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E2">
         <f>SUM(IU2,IY2,JC2,JG2,JK2,JO2,JS2,JW2,KA2,KE2,KI2,KM2,KQ2,KU2,KY2,LC2,LG2,LK2,LO2,LS2,LW2,MA2,ME2,MI2,MM2,MQ2,MU2,MY2,NC2,NG2,NK2,NO2,NS2,NW2,OA2,OE2,OI2,OM2,OQ2,OU2,OY2,PC2,PG2,PK2,PO2)</f>
@@ -2234,11 +2234,11 @@
       </c>
       <c r="G2">
         <f>SUM(H2:I2)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" s="3">
         <f>COUNTIF(AI2:PR2,"T")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3">
         <f>COUNTIF(AI2:PR2,"R")</f>
@@ -2250,11 +2250,11 @@
       </c>
       <c r="K2">
         <f>SUM(L2:M2)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="3">
         <f>COUNTIF(CY2:GX2,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" s="3">
         <f>COUNTIF(CY2:GX2,"R")</f>
@@ -2266,11 +2266,11 @@
       </c>
       <c r="O2">
         <f>SUM(P2:Q2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" s="3">
         <f>COUNTIF(GY2:IT2,"T")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="3">
         <f>COUNTIF(GY2:IT2,"R")</f>
@@ -2392,6 +2392,12 @@
       <c r="DT2" t="s">
         <v>141</v>
       </c>
+      <c r="DW2">
+        <v>90</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>141</v>
+      </c>
       <c r="HD2" t="s">
         <v>151</v>
       </c>
@@ -2399,6 +2405,12 @@
         <v>90</v>
       </c>
       <c r="HH2" t="s">
+        <v>141</v>
+      </c>
+      <c r="HK2">
+        <v>90</v>
+      </c>
+      <c r="HL2" t="s">
         <v>141</v>
       </c>
       <c r="PS2" s="3">
@@ -2460,7 +2472,7 @@
       </c>
       <c r="J3" s="3">
         <f t="shared" ref="J3:J28" si="12">COUNTIF(AI3:PR3,"NR")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:K28" si="13">SUM(L3:M3)</f>
@@ -2476,7 +2488,7 @@
       </c>
       <c r="N3" s="3">
         <f t="shared" ref="N3:N28" si="16">COUNTIF(CY3:GX3,"NR")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O28" si="17">SUM(P3:Q3)</f>
@@ -2492,7 +2504,7 @@
       </c>
       <c r="R3" s="3">
         <f t="shared" ref="R3:R28" si="20">COUNTIF(GY3:IT3,"NR")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <f t="shared" ref="S3:S28" si="21">SUM(T3:U3)</f>
@@ -2582,6 +2594,9 @@
       <c r="DT3" t="s">
         <v>149</v>
       </c>
+      <c r="DX3" t="s">
+        <v>151</v>
+      </c>
       <c r="HC3">
         <v>90</v>
       </c>
@@ -2589,6 +2604,9 @@
         <v>141</v>
       </c>
       <c r="HH3" t="s">
+        <v>151</v>
+      </c>
+      <c r="HL3" t="s">
         <v>151</v>
       </c>
       <c r="PS3" s="3">
@@ -2790,23 +2808,29 @@
       <c r="DT4" t="s">
         <v>149</v>
       </c>
+      <c r="DX4" t="s">
+        <v>149</v>
+      </c>
       <c r="HD4" t="s">
         <v>149</v>
       </c>
       <c r="HH4" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL4" t="s">
         <v>149</v>
       </c>
       <c r="PS4" s="3">
         <f t="shared" ref="PS4" si="57">COUNTIF(AI4:PR4,"HG")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT4" s="3">
         <f t="shared" ref="PT4" si="58">COUNTIF(CY4:GX4,"HG")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU4" s="3">
         <f t="shared" ref="PU4" si="59">COUNTIF(GY4:IT4,"HG")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV4">
         <f t="shared" si="4"/>
@@ -2823,7 +2847,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="36"/>
-        <v>707</v>
+        <v>797</v>
       </c>
       <c r="C5">
         <f t="shared" si="5"/>
@@ -2831,7 +2855,7 @@
       </c>
       <c r="D5">
         <f t="shared" si="6"/>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E5">
         <f t="shared" si="7"/>
@@ -2843,11 +2867,11 @@
       </c>
       <c r="G5">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="11"/>
@@ -2875,11 +2899,11 @@
       </c>
       <c r="O5">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="3">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="19"/>
@@ -3007,6 +3031,9 @@
       <c r="DT5" t="s">
         <v>142</v>
       </c>
+      <c r="DX5" t="s">
+        <v>149</v>
+      </c>
       <c r="HC5">
         <v>90</v>
       </c>
@@ -3019,13 +3046,19 @@
       <c r="HH5" t="s">
         <v>141</v>
       </c>
+      <c r="HK5">
+        <v>90</v>
+      </c>
+      <c r="HL5" t="s">
+        <v>141</v>
+      </c>
       <c r="PS5" s="3">
         <f t="shared" si="32"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PT5" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU5" s="3">
         <f t="shared" si="34"/>
@@ -3046,15 +3079,15 @@
       </c>
       <c r="B6">
         <f t="shared" si="36"/>
-        <v>619</v>
+        <v>799</v>
       </c>
       <c r="C6">
         <f t="shared" si="5"/>
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="D6">
         <f t="shared" si="6"/>
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E6">
         <f t="shared" si="7"/>
@@ -3066,11 +3099,11 @@
       </c>
       <c r="G6">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="11"/>
@@ -3082,11 +3115,11 @@
       </c>
       <c r="K6">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" s="3">
         <f t="shared" si="15"/>
@@ -3098,11 +3131,11 @@
       </c>
       <c r="O6">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" s="3">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3">
         <f t="shared" si="19"/>
@@ -3245,6 +3278,12 @@
       <c r="DT6" t="s">
         <v>141</v>
       </c>
+      <c r="DW6">
+        <v>90</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>141</v>
+      </c>
       <c r="HC6">
         <v>90</v>
       </c>
@@ -3256,6 +3295,12 @@
       </c>
       <c r="HH6" t="s">
         <v>142</v>
+      </c>
+      <c r="HK6">
+        <v>90</v>
+      </c>
+      <c r="HL6" t="s">
+        <v>141</v>
       </c>
       <c r="PS6" s="3">
         <f t="shared" si="32"/>
@@ -3438,23 +3483,29 @@
       <c r="DT7" t="s">
         <v>149</v>
       </c>
+      <c r="DX7" t="s">
+        <v>149</v>
+      </c>
       <c r="HD7" t="s">
         <v>149</v>
       </c>
       <c r="HH7" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL7" t="s">
         <v>149</v>
       </c>
       <c r="PS7" s="3">
         <f t="shared" si="32"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT7" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU7" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV7">
         <f t="shared" si="4"/>
@@ -3646,23 +3697,29 @@
       <c r="DT8" t="s">
         <v>149</v>
       </c>
+      <c r="DX8" t="s">
+        <v>149</v>
+      </c>
       <c r="HD8" t="s">
         <v>149</v>
       </c>
       <c r="HH8" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL8" t="s">
         <v>149</v>
       </c>
       <c r="PS8" s="3">
         <f t="shared" si="32"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="PT8" s="3">
         <f t="shared" si="33"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU8" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV8">
         <f t="shared" si="4"/>
@@ -3679,15 +3736,15 @@
       </c>
       <c r="B9">
         <f t="shared" si="36"/>
-        <v>863</v>
+        <v>1043</v>
       </c>
       <c r="C9">
         <f t="shared" si="5"/>
-        <v>528</v>
+        <v>618</v>
       </c>
       <c r="D9">
         <f t="shared" si="6"/>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E9">
         <f t="shared" si="7"/>
@@ -3699,11 +3756,11 @@
       </c>
       <c r="G9">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I9" s="3">
         <f t="shared" si="11"/>
@@ -3715,11 +3772,11 @@
       </c>
       <c r="K9">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3">
         <f t="shared" si="14"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9" s="3">
         <f t="shared" si="15"/>
@@ -3731,11 +3788,11 @@
       </c>
       <c r="O9">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="3">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="19"/>
@@ -3869,6 +3926,12 @@
       <c r="DT9" t="s">
         <v>141</v>
       </c>
+      <c r="DW9">
+        <v>90</v>
+      </c>
+      <c r="DX9" t="s">
+        <v>141</v>
+      </c>
       <c r="HD9" t="s">
         <v>149</v>
       </c>
@@ -3876,6 +3939,12 @@
         <v>90</v>
       </c>
       <c r="HH9" t="s">
+        <v>141</v>
+      </c>
+      <c r="HK9">
+        <v>90</v>
+      </c>
+      <c r="HL9" t="s">
         <v>141</v>
       </c>
       <c r="PS9" s="3">
@@ -3905,15 +3974,15 @@
       </c>
       <c r="B10">
         <f t="shared" si="36"/>
-        <v>806</v>
+        <v>966</v>
       </c>
       <c r="C10">
         <f t="shared" si="5"/>
-        <v>384</v>
+        <v>474</v>
       </c>
       <c r="D10">
         <f t="shared" si="6"/>
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="E10">
         <f t="shared" si="7"/>
@@ -3925,11 +3994,11 @@
       </c>
       <c r="G10">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I10" s="3">
         <f t="shared" si="11"/>
@@ -3941,11 +4010,11 @@
       </c>
       <c r="K10">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" s="3">
         <f t="shared" si="14"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="3">
         <f t="shared" si="15"/>
@@ -3957,11 +4026,11 @@
       </c>
       <c r="O10">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" s="3">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="19"/>
@@ -4104,6 +4173,12 @@
       <c r="DT10" t="s">
         <v>142</v>
       </c>
+      <c r="DW10">
+        <v>90</v>
+      </c>
+      <c r="DX10" t="s">
+        <v>141</v>
+      </c>
       <c r="HC10">
         <v>90</v>
       </c>
@@ -4115,6 +4190,12 @@
       </c>
       <c r="HH10" t="s">
         <v>142</v>
+      </c>
+      <c r="HK10">
+        <v>70</v>
+      </c>
+      <c r="HL10" t="s">
+        <v>141</v>
       </c>
       <c r="PS10" s="3">
         <f t="shared" si="32"/>
@@ -4143,15 +4224,15 @@
       </c>
       <c r="B11">
         <f t="shared" si="36"/>
-        <v>914</v>
+        <v>1079</v>
       </c>
       <c r="C11">
         <f t="shared" si="5"/>
-        <v>424</v>
+        <v>499</v>
       </c>
       <c r="D11">
         <f t="shared" si="6"/>
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="E11">
         <f t="shared" si="7"/>
@@ -4163,11 +4244,11 @@
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" si="11"/>
@@ -4179,11 +4260,11 @@
       </c>
       <c r="K11">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L11" s="3">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" s="3">
         <f t="shared" si="15"/>
@@ -4195,11 +4276,11 @@
       </c>
       <c r="O11">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" s="3">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="19"/>
@@ -4227,23 +4308,23 @@
       </c>
       <c r="W11" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X11" s="4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB11">
         <f t="shared" si="26"/>
@@ -4255,7 +4336,7 @@
       </c>
       <c r="AD11">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11">
         <f t="shared" si="29"/>
@@ -4345,6 +4426,15 @@
       <c r="DT11" t="s">
         <v>141</v>
       </c>
+      <c r="DW11">
+        <v>75</v>
+      </c>
+      <c r="DX11" t="s">
+        <v>141</v>
+      </c>
+      <c r="DY11">
+        <v>1</v>
+      </c>
       <c r="HC11">
         <v>90</v>
       </c>
@@ -4361,6 +4451,15 @@
         <v>141</v>
       </c>
       <c r="HI11">
+        <v>1</v>
+      </c>
+      <c r="HK11">
+        <v>90</v>
+      </c>
+      <c r="HL11" t="s">
+        <v>141</v>
+      </c>
+      <c r="HN11">
         <v>1</v>
       </c>
       <c r="PS11" s="3">
@@ -4390,11 +4489,11 @@
       </c>
       <c r="B12">
         <f t="shared" si="36"/>
-        <v>448</v>
+        <v>538</v>
       </c>
       <c r="C12">
         <f t="shared" si="5"/>
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="D12">
         <f t="shared" si="6"/>
@@ -4410,11 +4509,11 @@
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="3">
         <f t="shared" si="11"/>
@@ -4426,11 +4525,11 @@
       </c>
       <c r="K12">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" s="3">
         <f t="shared" si="15"/>
@@ -4559,6 +4658,12 @@
       <c r="DT12" t="s">
         <v>141</v>
       </c>
+      <c r="DW12">
+        <v>90</v>
+      </c>
+      <c r="DX12" t="s">
+        <v>141</v>
+      </c>
       <c r="HC12">
         <v>79</v>
       </c>
@@ -4571,9 +4676,12 @@
       <c r="HH12" t="s">
         <v>141</v>
       </c>
+      <c r="HL12" t="s">
+        <v>149</v>
+      </c>
       <c r="PS12" s="3">
         <f t="shared" si="32"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="PT12" s="3">
         <f t="shared" si="33"/>
@@ -4581,7 +4689,7 @@
       </c>
       <c r="PU12" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV12">
         <f t="shared" si="4"/>
@@ -4598,15 +4706,15 @@
       </c>
       <c r="B13">
         <f t="shared" si="36"/>
-        <v>451</v>
+        <v>622</v>
       </c>
       <c r="C13">
         <f t="shared" si="5"/>
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="D13">
         <f t="shared" si="6"/>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E13">
         <f t="shared" si="7"/>
@@ -4618,11 +4726,11 @@
       </c>
       <c r="G13">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="10"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="11"/>
@@ -4634,11 +4742,11 @@
       </c>
       <c r="K13">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13" s="3">
         <f t="shared" si="14"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M13" s="3">
         <f t="shared" si="15"/>
@@ -4650,11 +4758,11 @@
       </c>
       <c r="O13">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" s="3">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="3">
         <f t="shared" si="19"/>
@@ -4682,11 +4790,11 @@
       </c>
       <c r="W13" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X13" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" s="4">
         <f t="shared" si="50"/>
@@ -4698,7 +4806,7 @@
       </c>
       <c r="AA13">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB13">
         <f t="shared" si="26"/>
@@ -4706,7 +4814,7 @@
       </c>
       <c r="AC13">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13">
         <f t="shared" si="28"/>
@@ -4791,6 +4899,15 @@
       <c r="DT13" t="s">
         <v>141</v>
       </c>
+      <c r="DW13">
+        <v>81</v>
+      </c>
+      <c r="DX13" t="s">
+        <v>141</v>
+      </c>
+      <c r="DY13">
+        <v>1</v>
+      </c>
       <c r="HC13">
         <v>90</v>
       </c>
@@ -4799,6 +4916,15 @@
       </c>
       <c r="HH13" t="s">
         <v>149</v>
+      </c>
+      <c r="HK13">
+        <v>90</v>
+      </c>
+      <c r="HL13" t="s">
+        <v>141</v>
+      </c>
+      <c r="HM13">
+        <v>1</v>
       </c>
       <c r="PS13" s="3">
         <f t="shared" si="32"/>
@@ -4827,11 +4953,11 @@
       </c>
       <c r="B14">
         <f t="shared" si="36"/>
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="C14">
         <f t="shared" si="5"/>
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D14">
         <f t="shared" si="6"/>
@@ -4847,7 +4973,7 @@
       </c>
       <c r="G14">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="10"/>
@@ -4855,7 +4981,7 @@
       </c>
       <c r="I14" s="3">
         <f t="shared" si="11"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="3">
         <f t="shared" si="12"/>
@@ -4863,7 +4989,7 @@
       </c>
       <c r="K14">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L14" s="3">
         <f t="shared" si="14"/>
@@ -4871,7 +4997,7 @@
       </c>
       <c r="M14" s="3">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <f t="shared" si="16"/>
@@ -5023,6 +5149,12 @@
       <c r="DT14" t="s">
         <v>142</v>
       </c>
+      <c r="DW14">
+        <v>9</v>
+      </c>
+      <c r="DX14" t="s">
+        <v>142</v>
+      </c>
       <c r="HC14">
         <v>75</v>
       </c>
@@ -5035,9 +5167,12 @@
       <c r="HH14" t="s">
         <v>141</v>
       </c>
+      <c r="HL14" t="s">
+        <v>149</v>
+      </c>
       <c r="PS14" s="3">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PT14" s="3">
         <f t="shared" si="33"/>
@@ -5045,7 +5180,7 @@
       </c>
       <c r="PU14" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV14">
         <f t="shared" si="4"/>
@@ -5246,23 +5381,29 @@
       <c r="DT15" t="s">
         <v>149</v>
       </c>
+      <c r="DX15" t="s">
+        <v>149</v>
+      </c>
       <c r="HD15" t="s">
         <v>149</v>
       </c>
       <c r="HH15" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL15" t="s">
         <v>149</v>
       </c>
       <c r="PS15" s="3">
         <f t="shared" si="32"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT15" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU15" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV15">
         <f t="shared" si="4"/>
@@ -5442,6 +5583,9 @@
       <c r="DT16" t="s">
         <v>149</v>
       </c>
+      <c r="DX16" t="s">
+        <v>149</v>
+      </c>
       <c r="HD16" t="s">
         <v>149</v>
       </c>
@@ -5451,17 +5595,20 @@
       <c r="HH16" t="s">
         <v>142</v>
       </c>
+      <c r="HL16" t="s">
+        <v>149</v>
+      </c>
       <c r="PS16" s="3">
         <f t="shared" si="32"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="PT16" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU16" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PV16">
         <f t="shared" si="4"/>
@@ -5677,23 +5824,29 @@
       <c r="DT17" t="s">
         <v>149</v>
       </c>
+      <c r="DX17" t="s">
+        <v>149</v>
+      </c>
       <c r="HD17" t="s">
         <v>149</v>
       </c>
       <c r="HH17" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL17" t="s">
         <v>149</v>
       </c>
       <c r="PS17" s="3">
         <f t="shared" si="32"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="PT17" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU17" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV17">
         <f t="shared" si="4"/>
@@ -5710,15 +5863,15 @@
       </c>
       <c r="B18">
         <f t="shared" si="36"/>
-        <v>602</v>
+        <v>696</v>
       </c>
       <c r="C18">
         <f t="shared" si="5"/>
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D18">
         <f t="shared" si="6"/>
-        <v>173</v>
+        <v>248</v>
       </c>
       <c r="E18">
         <f t="shared" si="7"/>
@@ -5730,15 +5883,15 @@
       </c>
       <c r="G18">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="10"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="3">
         <f t="shared" si="12"/>
@@ -5746,7 +5899,7 @@
       </c>
       <c r="K18">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L18" s="3">
         <f t="shared" si="14"/>
@@ -5754,7 +5907,7 @@
       </c>
       <c r="M18" s="3">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N18" s="3">
         <f t="shared" si="16"/>
@@ -5762,11 +5915,11 @@
       </c>
       <c r="O18">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P18" s="3">
         <f t="shared" si="18"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="3">
         <f t="shared" si="19"/>
@@ -5906,6 +6059,12 @@
       <c r="DT18" t="s">
         <v>141</v>
       </c>
+      <c r="DW18">
+        <v>19</v>
+      </c>
+      <c r="DX18" t="s">
+        <v>142</v>
+      </c>
       <c r="HC18">
         <v>83</v>
       </c>
@@ -5919,6 +6078,12 @@
         <v>90</v>
       </c>
       <c r="HH18" t="s">
+        <v>141</v>
+      </c>
+      <c r="HK18">
+        <v>75</v>
+      </c>
+      <c r="HL18" t="s">
         <v>141</v>
       </c>
       <c r="PS18" s="3">
@@ -6150,6 +6315,9 @@
       <c r="DT19" t="s">
         <v>149</v>
       </c>
+      <c r="DX19" t="s">
+        <v>149</v>
+      </c>
       <c r="HC19">
         <v>15</v>
       </c>
@@ -6159,17 +6327,20 @@
       <c r="HH19" t="s">
         <v>149</v>
       </c>
+      <c r="HL19" t="s">
+        <v>149</v>
+      </c>
       <c r="PS19" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PT19" s="3">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PU19" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PV19">
         <f t="shared" si="4"/>
@@ -6364,23 +6535,29 @@
       <c r="DT20" t="s">
         <v>149</v>
       </c>
+      <c r="DX20" t="s">
+        <v>149</v>
+      </c>
       <c r="HD20" t="s">
         <v>149</v>
       </c>
       <c r="HH20" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL20" t="s">
         <v>149</v>
       </c>
       <c r="PS20" s="3">
         <f t="shared" si="32"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT20" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU20" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV20">
         <f t="shared" si="4"/>
@@ -6575,6 +6752,9 @@
       <c r="DT21" t="s">
         <v>149</v>
       </c>
+      <c r="DX21" t="s">
+        <v>149</v>
+      </c>
       <c r="HC21">
         <v>7</v>
       </c>
@@ -6584,17 +6764,20 @@
       <c r="HH21" t="s">
         <v>149</v>
       </c>
+      <c r="HL21" t="s">
+        <v>149</v>
+      </c>
       <c r="PS21" s="3">
         <f t="shared" si="32"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="PT21" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU21" s="3">
         <f t="shared" si="34"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="PV21">
         <f t="shared" si="4"/>
@@ -6798,23 +6981,29 @@
       <c r="DT22" t="s">
         <v>149</v>
       </c>
+      <c r="DX22" t="s">
+        <v>149</v>
+      </c>
       <c r="HD22" t="s">
         <v>149</v>
       </c>
       <c r="HH22" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL22" t="s">
         <v>149</v>
       </c>
       <c r="PS22" s="3">
         <f t="shared" si="32"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT22" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU22" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV22">
         <f t="shared" si="4"/>
@@ -6831,15 +7020,15 @@
       </c>
       <c r="B23">
         <f t="shared" si="36"/>
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C23">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E23">
         <f t="shared" si="7"/>
@@ -6851,7 +7040,7 @@
       </c>
       <c r="G23">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="10"/>
@@ -6859,7 +7048,7 @@
       </c>
       <c r="I23" s="3">
         <f t="shared" si="11"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J23" s="3">
         <f t="shared" si="12"/>
@@ -6867,7 +7056,7 @@
       </c>
       <c r="K23">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="14"/>
@@ -6875,7 +7064,7 @@
       </c>
       <c r="M23" s="3">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="3">
         <f t="shared" si="16"/>
@@ -6883,7 +7072,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="3">
         <f t="shared" si="18"/>
@@ -6891,7 +7080,7 @@
       </c>
       <c r="Q23" s="3">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="3">
         <f t="shared" si="20"/>
@@ -7012,11 +7201,23 @@
       <c r="DT23" t="s">
         <v>149</v>
       </c>
+      <c r="DW23">
+        <v>9</v>
+      </c>
+      <c r="DX23" t="s">
+        <v>142</v>
+      </c>
       <c r="HD23" t="s">
         <v>149</v>
       </c>
       <c r="HH23" t="s">
         <v>149</v>
+      </c>
+      <c r="HK23">
+        <v>20</v>
+      </c>
+      <c r="HL23" t="s">
+        <v>142</v>
       </c>
       <c r="PS23" s="3">
         <f t="shared" si="32"/>
@@ -7232,23 +7433,29 @@
       <c r="DT24" t="s">
         <v>149</v>
       </c>
+      <c r="DX24" t="s">
+        <v>149</v>
+      </c>
       <c r="HD24" t="s">
         <v>149</v>
       </c>
       <c r="HH24" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL24" t="s">
         <v>149</v>
       </c>
       <c r="PS24" s="3">
         <f t="shared" si="32"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="PT24" s="3">
         <f t="shared" si="33"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="PU24" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV24">
         <f t="shared" si="4"/>
@@ -7265,15 +7472,15 @@
       </c>
       <c r="B25">
         <f t="shared" si="36"/>
-        <v>782</v>
+        <v>938</v>
       </c>
       <c r="C25">
         <f t="shared" si="5"/>
-        <v>434</v>
+        <v>515</v>
       </c>
       <c r="D25">
         <f t="shared" si="6"/>
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="E25">
         <f t="shared" si="7"/>
@@ -7285,11 +7492,11 @@
       </c>
       <c r="G25">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="10"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I25" s="3">
         <f t="shared" si="11"/>
@@ -7301,11 +7508,11 @@
       </c>
       <c r="K25">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25" s="3">
         <f t="shared" si="15"/>
@@ -7317,11 +7524,11 @@
       </c>
       <c r="O25">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P25" s="3">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="3">
         <f t="shared" si="19"/>
@@ -7349,11 +7556,11 @@
       </c>
       <c r="W25" s="3">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X25" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y25" s="4">
         <f t="shared" si="50"/>
@@ -7365,7 +7572,7 @@
       </c>
       <c r="AA25">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
         <f t="shared" si="26"/>
@@ -7461,6 +7668,15 @@
       <c r="DT25" t="s">
         <v>141</v>
       </c>
+      <c r="DW25">
+        <v>81</v>
+      </c>
+      <c r="DX25" t="s">
+        <v>141</v>
+      </c>
+      <c r="DY25">
+        <v>1</v>
+      </c>
       <c r="HC25">
         <v>90</v>
       </c>
@@ -7475,6 +7691,12 @@
       </c>
       <c r="HH25" t="s">
         <v>142</v>
+      </c>
+      <c r="HK25">
+        <v>75</v>
+      </c>
+      <c r="HL25" t="s">
+        <v>141</v>
       </c>
       <c r="PS25" s="3">
         <f t="shared" si="32"/>
@@ -7672,6 +7894,9 @@
       <c r="DT26" t="s">
         <v>142</v>
       </c>
+      <c r="DX26" t="s">
+        <v>149</v>
+      </c>
       <c r="HC26">
         <v>75</v>
       </c>
@@ -7687,17 +7912,20 @@
       <c r="HH26" t="s">
         <v>141</v>
       </c>
+      <c r="HL26" t="s">
+        <v>149</v>
+      </c>
       <c r="PS26" s="3">
         <f t="shared" si="32"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="PT26" s="3">
         <f t="shared" si="33"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PU26" s="3">
         <f t="shared" si="34"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="PV26">
         <f t="shared" si="4"/>
@@ -7880,23 +8108,29 @@
       <c r="DT27" t="s">
         <v>149</v>
       </c>
+      <c r="DX27" t="s">
+        <v>149</v>
+      </c>
       <c r="HD27" t="s">
         <v>149</v>
       </c>
       <c r="HH27" t="s">
+        <v>149</v>
+      </c>
+      <c r="HL27" t="s">
         <v>149</v>
       </c>
       <c r="PS27" s="3">
         <f t="shared" si="32"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="PT27" s="3">
         <f t="shared" si="33"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="PU27" s="3">
         <f t="shared" si="34"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="PV27">
         <f t="shared" si="4"/>
@@ -7913,15 +8147,15 @@
       </c>
       <c r="B28">
         <f t="shared" si="36"/>
-        <v>867</v>
+        <v>972</v>
       </c>
       <c r="C28">
         <f t="shared" si="5"/>
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E28">
         <f t="shared" si="7"/>
@@ -7933,15 +8167,15 @@
       </c>
       <c r="G28">
         <f t="shared" si="9"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="10"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="3">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="3">
         <f t="shared" si="12"/>
@@ -7949,11 +8183,11 @@
       </c>
       <c r="K28">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="14"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M28" s="3">
         <f t="shared" si="15"/>
@@ -7965,7 +8199,7 @@
       </c>
       <c r="O28">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" s="3">
         <f t="shared" si="18"/>
@@ -7973,7 +8207,7 @@
       </c>
       <c r="Q28" s="3">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" s="3">
         <f t="shared" si="20"/>
@@ -8109,6 +8343,12 @@
       <c r="DT28" t="s">
         <v>141</v>
       </c>
+      <c r="DW28">
+        <v>90</v>
+      </c>
+      <c r="DX28" t="s">
+        <v>141</v>
+      </c>
       <c r="HC28">
         <v>15</v>
       </c>
@@ -8120,6 +8360,12 @@
       </c>
       <c r="HH28" t="s">
         <v>141</v>
+      </c>
+      <c r="HK28">
+        <v>15</v>
+      </c>
+      <c r="HL28" t="s">
+        <v>142</v>
       </c>
       <c r="PS28" s="3">
         <f t="shared" si="32"/>
@@ -8148,15 +8394,15 @@
       </c>
       <c r="B29">
         <f t="shared" ref="B29" si="61">SUM(AI29,AM29,AQ29,AU29,AY29,BC29,BG29,BK29,BO29,BS29,BW29,CA29,CE29,CI29,CM29,CQ29,CU29,CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29,GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29,IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="C29">
         <f t="shared" ref="C29" si="62">SUM(CY29,DC29,DG29,DK29,DO29,DS29,DW29,EA29,EE29,EI29,EM29,EQ29,EU29,EY29,FC29,FG29,FK29,FO29,FS29,FW29,GA29,GE29,GI29,GM29,GQ29,GU29)</f>
-        <v>525</v>
+        <v>615</v>
       </c>
       <c r="D29">
         <f t="shared" ref="D29" si="63">SUM(GY29,HC29,HG29,HK29,HO29,HS29,HW29,IA29,IE29,II29,IM29,IQ29)</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E29">
         <f t="shared" ref="E29" si="64">SUM(IU29,IY29,JC29,JG29,JK29,JO29,JS29,JW29,KA29,KE29,KI29,KM29,KQ29,KU29,KY29,LC29,LG29,LK29,LO29,LS29,LW29,MA29,ME29,MI29,MM29,MQ29,MU29,MY29,NC29,NG29,NK29,NO29,NS29,NW29,OA29,OE29,OI29,OM29,OQ29,OU29,OY29,PC29,PG29,PK29,PO29)</f>
@@ -8168,11 +8414,11 @@
       </c>
       <c r="G29">
         <f t="shared" ref="G29" si="65">SUM(H29:I29)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" ref="H29" si="66">COUNTIF(AI29:PR29,"T")</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I29" s="3">
         <f t="shared" ref="I29" si="67">COUNTIF(AI29:PR29,"R")</f>
@@ -8184,11 +8430,11 @@
       </c>
       <c r="K29">
         <f t="shared" ref="K29" si="69">SUM(L29:M29)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" ref="L29" si="70">COUNTIF(CY29:GX29,"T")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="3">
         <f t="shared" ref="M29" si="71">COUNTIF(CY29:GX29,"R")</f>
@@ -8200,11 +8446,11 @@
       </c>
       <c r="O29">
         <f t="shared" ref="O29" si="73">SUM(P29:Q29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="3">
         <f t="shared" ref="P29" si="74">COUNTIF(GY29:IT29,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="3">
         <f t="shared" ref="Q29" si="75">COUNTIF(GY29:IT29,"R")</f>
@@ -8240,11 +8486,11 @@
       </c>
       <c r="Y29" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29">
         <f t="shared" ref="AA29" si="80">SUM(DA29,DE29,DI29,DM29,DQ29,DU29,DY29,EC29,EG29,EK29,EO29,ES29,EW29,FA29,FE29,FI29,FM29,FQ29,FU29,FY29,GC29,GG29,GK29,GO29,GS29,GW29)</f>
@@ -8252,7 +8498,7 @@
       </c>
       <c r="AB29">
         <f t="shared" ref="AB29" si="81">SUM(DB29,DF29,DJ29,DN29,DR29,DV29,DZ29,ED29,EH29,EL29,EP29,ET29,EX29,FB29,FF29,FJ29,FN29,FR29,FV29,FZ29,GD29,GH29,GL29,GP29,GT29,GX29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29">
         <f t="shared" ref="AC29" si="82">SUM(HA29,HE29,HI29,HM29,HQ29,HU29,HY29,IC29,IG29,IK29,IO29,IS29)</f>
@@ -8350,11 +8596,26 @@
       <c r="DT29" t="s">
         <v>141</v>
       </c>
+      <c r="DW29">
+        <v>90</v>
+      </c>
+      <c r="DX29" t="s">
+        <v>141</v>
+      </c>
+      <c r="DZ29">
+        <v>1</v>
+      </c>
       <c r="HD29" t="s">
         <v>149</v>
       </c>
       <c r="HH29" t="s">
         <v>149</v>
+      </c>
+      <c r="HK29">
+        <v>90</v>
+      </c>
+      <c r="HL29" t="s">
+        <v>141</v>
       </c>
       <c r="PS29" s="3">
         <f t="shared" ref="PS29" si="86">COUNTIF(AI29:PR29,"HG")</f>
@@ -8383,15 +8644,15 @@
       </c>
       <c r="B30">
         <f t="shared" ref="B30" si="90">SUM(AI30,AM30,AQ30,AU30,AY30,BC30,BG30,BK30,BO30,BS30,BW30,CA30,CE30,CI30,CM30,CQ30,CU30,CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30,GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30,IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
-        <v>317</v>
+        <v>467</v>
       </c>
       <c r="C30">
         <f t="shared" ref="C30" si="91">SUM(CY30,DC30,DG30,DK30,DO30,DS30,DW30,EA30,EE30,EI30,EM30,EQ30,EU30,EY30,FC30,FG30,FK30,FO30,FS30,FW30,GA30,GE30,GI30,GM30,GQ30,GU30)</f>
-        <v>306</v>
+        <v>377</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30" si="92">SUM(GY30,HC30,HG30,HK30,HO30,HS30,HW30,IA30,IE30,II30,IM30,IQ30)</f>
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <f t="shared" ref="E30" si="93">SUM(IU30,IY30,JC30,JG30,JK30,JO30,JS30,JW30,KA30,KE30,KI30,KM30,KQ30,KU30,KY30,LC30,LG30,LK30,LO30,LS30,LW30,MA30,ME30,MI30,MM30,MQ30,MU30,MY30,NC30,NG30,NK30,NO30,NS30,NW30,OA30,OE30,OI30,OM30,OQ30,OU30,OY30,PC30,PG30,PK30,PO30)</f>
@@ -8403,11 +8664,11 @@
       </c>
       <c r="G30">
         <f t="shared" ref="G30" si="95">SUM(H30:I30)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" ref="H30" si="96">COUNTIF(AI30:PR30,"T")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" s="3">
         <f t="shared" ref="I30" si="97">COUNTIF(AI30:PR30,"R")</f>
@@ -8419,11 +8680,11 @@
       </c>
       <c r="K30">
         <f t="shared" ref="K30" si="99">SUM(L30:M30)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" ref="L30" si="100">COUNTIF(CY30:GX30,"T")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M30" s="3">
         <f t="shared" ref="M30" si="101">COUNTIF(CY30:GX30,"R")</f>
@@ -8435,11 +8696,11 @@
       </c>
       <c r="O30">
         <f t="shared" ref="O30" si="103">SUM(P30:Q30)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" s="3">
         <f t="shared" ref="P30" si="104">COUNTIF(GY30:IT30,"T")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="3">
         <f t="shared" ref="Q30" si="105">COUNTIF(GY30:IT30,"R")</f>
@@ -8475,11 +8736,11 @@
       </c>
       <c r="Y30" s="4">
         <f t="shared" si="50"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z30" s="4">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30">
         <f t="shared" ref="AA30" si="110">SUM(DA30,DE30,DI30,DM30,DQ30,DU30,DY30,EC30,EG30,EK30,EO30,ES30,EW30,FA30,FE30,FI30,FM30,FQ30,FU30,FY30,GC30,GG30,GK30,GO30,GS30,GW30)</f>
@@ -8487,7 +8748,7 @@
       </c>
       <c r="AB30">
         <f t="shared" ref="AB30" si="111">SUM(DB30,DF30,DJ30,DN30,DR30,DV30,DZ30,ED30,EH30,EL30,EP30,ET30,EX30,FB30,FF30,FJ30,FN30,FR30,FV30,FZ30,GD30,GH30,GL30,GP30,GT30,GX30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30">
         <f t="shared" ref="AC30" si="112">SUM(HA30,HE30,HI30,HM30,HQ30,HU30,HY30,IC30,IG30,IK30,IO30,IS30)</f>
@@ -8549,6 +8810,15 @@
       <c r="DT30" t="s">
         <v>141</v>
       </c>
+      <c r="DW30">
+        <v>71</v>
+      </c>
+      <c r="DX30" t="s">
+        <v>141</v>
+      </c>
+      <c r="DZ30">
+        <v>1</v>
+      </c>
       <c r="HC30">
         <v>11</v>
       </c>
@@ -8557,6 +8827,12 @@
       </c>
       <c r="HH30" t="s">
         <v>149</v>
+      </c>
+      <c r="HK30">
+        <v>79</v>
+      </c>
+      <c r="HL30" t="s">
+        <v>141</v>
       </c>
       <c r="PS30" s="3">
         <f t="shared" ref="PS30" si="116">COUNTIF(AI30:PR30,"HG")</f>
@@ -8585,7 +8861,7 @@
       </c>
       <c r="B31">
         <f t="shared" ref="B31" si="120">SUM(AI31,AM31,AQ31,AU31,AY31,BC31,BG31,BK31,BO31,BS31,BW31,CA31,CE31,CI31,CM31,CQ31,CU31,CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31,GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31,IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C31">
         <f t="shared" ref="C31" si="121">SUM(CY31,DC31,DG31,DK31,DO31,DS31,DW31,EA31,EE31,EI31,EM31,EQ31,EU31,EY31,FC31,FG31,FK31,FO31,FS31,FW31,GA31,GE31,GI31,GM31,GQ31,GU31)</f>
@@ -8593,7 +8869,7 @@
       </c>
       <c r="D31">
         <f t="shared" ref="D31" si="122">SUM(GY31,HC31,HG31,HK31,HO31,HS31,HW31,IA31,IE31,II31,IM31,IQ31)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E31">
         <f t="shared" ref="E31" si="123">SUM(IU31,IY31,JC31,JG31,JK31,JO31,JS31,JW31,KA31,KE31,KI31,KM31,KQ31,KU31,KY31,LC31,LG31,LK31,LO31,LS31,LW31,MA31,ME31,MI31,MM31,MQ31,MU31,MY31,NC31,NG31,NK31,NO31,NS31,NW31,OA31,OE31,OI31,OM31,OQ31,OU31,OY31,PC31,PG31,PK31,PO31)</f>
@@ -8605,7 +8881,7 @@
       </c>
       <c r="G31">
         <f t="shared" ref="G31" si="125">SUM(H31:I31)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" ref="H31" si="126">COUNTIF(AI31:PR31,"T")</f>
@@ -8613,7 +8889,7 @@
       </c>
       <c r="I31" s="3">
         <f t="shared" ref="I31" si="127">COUNTIF(AI31:PR31,"R")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3">
         <f t="shared" ref="J31" si="128">COUNTIF(AI31:PR31,"NR")</f>
@@ -8637,7 +8913,7 @@
       </c>
       <c r="O31">
         <f t="shared" ref="O31:O33" si="133">SUM(P31:Q31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="3">
         <f t="shared" ref="P31:P33" si="134">COUNTIF(GY31:IT31,"T")</f>
@@ -8645,7 +8921,7 @@
       </c>
       <c r="Q31" s="3">
         <f t="shared" ref="Q31:Q33" si="135">COUNTIF(GY31:IT31,"R")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="3">
         <f t="shared" ref="R31:R33" si="136">COUNTIF(GY31:IT31,"NR")</f>
@@ -8736,19 +9012,28 @@
       <c r="DT31" t="s">
         <v>149</v>
       </c>
+      <c r="DX31" t="s">
+        <v>149</v>
+      </c>
       <c r="HD31" t="s">
         <v>149</v>
       </c>
       <c r="HH31" t="s">
         <v>149</v>
+      </c>
+      <c r="HK31">
+        <v>11</v>
+      </c>
+      <c r="HL31" t="s">
+        <v>142</v>
       </c>
       <c r="PS31" s="3">
         <f t="shared" ref="PS31" si="146">COUNTIF(AI31:PR31,"HG")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="PT31" s="3">
         <f t="shared" ref="PT31" si="147">COUNTIF(CY31:GX31,"HG")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="PU31" s="3">
         <f t="shared" ref="PU31:PU33" si="148">COUNTIF(GY31:IT31,"HG")</f>
@@ -8804,6 +9089,12 @@
       <c r="DT32" t="s">
         <v>142</v>
       </c>
+      <c r="DW32">
+        <v>15</v>
+      </c>
+      <c r="DX32" t="s">
+        <v>142</v>
+      </c>
       <c r="HD32" t="s">
         <v>149</v>
       </c>
@@ -8813,9 +9104,12 @@
       <c r="HH32" t="s">
         <v>141</v>
       </c>
+      <c r="HL32" t="s">
+        <v>149</v>
+      </c>
       <c r="PU32">
         <f t="shared" si="148"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:437" x14ac:dyDescent="0.2">
@@ -8824,7 +9118,7 @@
       </c>
       <c r="O33">
         <f t="shared" si="133"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33">
         <f t="shared" si="134"/>
@@ -8832,7 +9126,7 @@
       </c>
       <c r="Q33">
         <f t="shared" si="135"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <f t="shared" si="136"/>
@@ -8849,6 +9143,12 @@
       </c>
       <c r="HI33">
         <v>1</v>
+      </c>
+      <c r="HK33">
+        <v>15</v>
+      </c>
+      <c r="HL33" t="s">
+        <v>142</v>
       </c>
       <c r="PU33">
         <f t="shared" si="148"/>
